--- a/FRTB SA Sensitivities/FRTB_Sensitivities.xlsx
+++ b/FRTB SA Sensitivities/FRTB_Sensitivities.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP64"/>
+  <dimension ref="A1:EQ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,7 @@
     <col width="5" customWidth="1" min="144" max="144"/>
     <col width="5" customWidth="1" min="145" max="145"/>
     <col width="5" customWidth="1" min="146" max="146"/>
+    <col width="5" customWidth="1" min="147" max="147"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -788,595 +789,600 @@
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
+          <t>GIRR_GBP_XCCY_BASIS</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
           <t>GIRR_USD_0.25Y</t>
         </is>
       </c>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_0.5Y</t>
         </is>
       </c>
-      <c r="AD2" s="3" t="inlineStr">
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_1.0Y</t>
         </is>
       </c>
-      <c r="AE2" s="3" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_2.0Y</t>
         </is>
       </c>
-      <c r="AF2" s="3" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_3.0Y</t>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_5.0Y</t>
         </is>
       </c>
-      <c r="AH2" s="3" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>GIRR_USD_10.0Y</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_3_0.5Y</t>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_3_1.0Y</t>
         </is>
       </c>
-      <c r="AK2" s="3" t="inlineStr">
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_3_3.0Y</t>
         </is>
       </c>
-      <c r="AL2" s="3" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_4_0.5Y</t>
         </is>
       </c>
-      <c r="AM2" s="3" t="inlineStr">
+      <c r="AN2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_4_1.0Y</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_4_3.0Y</t>
         </is>
       </c>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_4_5.0Y</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_5_0.5Y</t>
         </is>
       </c>
-      <c r="AQ2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_5_1.0Y</t>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_5_3.0Y</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_5_5.0Y</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_5_10.0Y</t>
         </is>
       </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_6_0.5Y</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_6_1.0Y</t>
         </is>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AX2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_6_3.0Y</t>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
+      <c r="AY2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_6_5.0Y</t>
         </is>
       </c>
-      <c r="AY2" s="3" t="inlineStr">
+      <c r="AZ2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_7_0.5Y</t>
         </is>
       </c>
-      <c r="AZ2" s="3" t="inlineStr">
+      <c r="BA2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_7_1.0Y</t>
         </is>
       </c>
-      <c r="BA2" s="3" t="inlineStr">
+      <c r="BB2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_7_3.0Y</t>
         </is>
       </c>
-      <c r="BB2" s="3" t="inlineStr">
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>CSR_NONSEC_7_5.0Y</t>
         </is>
       </c>
-      <c r="BC2" s="3" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_1_0.5Y</t>
         </is>
       </c>
-      <c r="BD2" s="3" t="inlineStr">
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_1_1.0Y</t>
         </is>
       </c>
-      <c r="BE2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_1_3.0Y</t>
         </is>
       </c>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BG2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_4_0.5Y</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BH2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_4_1.0Y</t>
         </is>
       </c>
-      <c r="BH2" s="3" t="inlineStr">
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_4_3.0Y</t>
         </is>
       </c>
-      <c r="BI2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_4_5.0Y</t>
         </is>
       </c>
-      <c r="BJ2" s="3" t="inlineStr">
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_4_10.0Y</t>
         </is>
       </c>
-      <c r="BK2" s="3" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_6_0.5Y</t>
         </is>
       </c>
-      <c r="BL2" s="3" t="inlineStr">
+      <c r="BM2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_6_1.0Y</t>
         </is>
       </c>
-      <c r="BM2" s="3" t="inlineStr">
+      <c r="BN2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_6_3.0Y</t>
         </is>
       </c>
-      <c r="BN2" s="3" t="inlineStr">
+      <c r="BO2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_6_5.0Y</t>
         </is>
       </c>
-      <c r="BO2" s="3" t="inlineStr">
+      <c r="BP2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_7_0.5Y</t>
         </is>
       </c>
-      <c r="BP2" s="3" t="inlineStr">
+      <c r="BQ2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_7_1.0Y</t>
         </is>
       </c>
-      <c r="BQ2" s="3" t="inlineStr">
+      <c r="BR2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_7_3.0Y</t>
         </is>
       </c>
-      <c r="BR2" s="3" t="inlineStr">
+      <c r="BS2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_7_5.0Y</t>
         </is>
       </c>
-      <c r="BS2" s="3" t="inlineStr">
+      <c r="BT2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_8_0.5Y</t>
         </is>
       </c>
-      <c r="BT2" s="3" t="inlineStr">
+      <c r="BU2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_8_1.0Y</t>
         </is>
       </c>
-      <c r="BU2" s="3" t="inlineStr">
+      <c r="BV2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_8_3.0Y</t>
         </is>
       </c>
-      <c r="BV2" s="3" t="inlineStr">
+      <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_8_5.0Y</t>
         </is>
       </c>
-      <c r="BW2" s="3" t="inlineStr">
+      <c r="BX2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_9_0.5Y</t>
         </is>
       </c>
-      <c r="BX2" s="3" t="inlineStr">
+      <c r="BY2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_9_1.0Y</t>
         </is>
       </c>
-      <c r="BY2" s="3" t="inlineStr">
+      <c r="BZ2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_9_3.0Y</t>
         </is>
       </c>
-      <c r="BZ2" s="3" t="inlineStr">
+      <c r="CA2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_12_0.5Y</t>
         </is>
       </c>
-      <c r="CA2" s="3" t="inlineStr">
+      <c r="CB2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_12_1.0Y</t>
         </is>
       </c>
-      <c r="CB2" s="3" t="inlineStr">
+      <c r="CC2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_12_3.0Y</t>
         </is>
       </c>
-      <c r="CC2" s="3" t="inlineStr">
+      <c r="CD2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_12_5.0Y</t>
         </is>
       </c>
-      <c r="CD2" s="3" t="inlineStr">
+      <c r="CE2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_12_10.0Y</t>
         </is>
       </c>
-      <c r="CE2" s="3" t="inlineStr">
+      <c r="CF2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_14_0.5Y</t>
         </is>
       </c>
-      <c r="CF2" s="3" t="inlineStr">
+      <c r="CG2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_14_1.0Y</t>
         </is>
       </c>
-      <c r="CG2" s="3" t="inlineStr">
+      <c r="CH2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_14_3.0Y</t>
         </is>
       </c>
-      <c r="CH2" s="3" t="inlineStr">
+      <c r="CI2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_14_5.0Y</t>
         </is>
       </c>
-      <c r="CI2" s="3" t="inlineStr">
+      <c r="CJ2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_15_0.5Y</t>
         </is>
       </c>
-      <c r="CJ2" s="3" t="inlineStr">
+      <c r="CK2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_15_1.0Y</t>
         </is>
       </c>
-      <c r="CK2" s="3" t="inlineStr">
+      <c r="CL2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_15_3.0Y</t>
         </is>
       </c>
-      <c r="CL2" s="3" t="inlineStr">
+      <c r="CM2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_15_5.0Y</t>
         </is>
       </c>
-      <c r="CM2" s="3" t="inlineStr">
+      <c r="CN2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_16_0.5Y</t>
         </is>
       </c>
-      <c r="CN2" s="3" t="inlineStr">
+      <c r="CO2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_16_1.0Y</t>
         </is>
       </c>
-      <c r="CO2" s="3" t="inlineStr">
+      <c r="CP2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_16_3.0Y</t>
         </is>
       </c>
-      <c r="CP2" s="3" t="inlineStr">
+      <c r="CQ2" s="3" t="inlineStr">
         <is>
           <t>CSR_SEC_NONCTP_16_5.0Y</t>
         </is>
       </c>
-      <c r="CQ2" s="3" t="inlineStr">
+      <c r="CR2" s="3" t="inlineStr">
         <is>
           <t>EQ_5_AMZN</t>
         </is>
       </c>
-      <c r="CR2" s="3" t="inlineStr">
+      <c r="CS2" s="3" t="inlineStr">
         <is>
           <t>EQ_7_XOM</t>
         </is>
       </c>
-      <c r="CS2" s="3" t="inlineStr">
+      <c r="CT2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_AAPL</t>
         </is>
       </c>
-      <c r="CT2" s="3" t="inlineStr">
+      <c r="CU2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_BRK.B</t>
         </is>
       </c>
-      <c r="CU2" s="3" t="inlineStr">
+      <c r="CV2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_EQIX</t>
         </is>
       </c>
-      <c r="CV2" s="3" t="inlineStr">
+      <c r="CW2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_GOOGL</t>
         </is>
       </c>
-      <c r="CW2" s="3" t="inlineStr">
+      <c r="CX2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_JPM</t>
         </is>
       </c>
-      <c r="CX2" s="3" t="inlineStr">
+      <c r="CY2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_META</t>
         </is>
       </c>
-      <c r="CY2" s="3" t="inlineStr">
+      <c r="CZ2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_MSFT</t>
         </is>
       </c>
-      <c r="CZ2" s="3" t="inlineStr">
+      <c r="DA2" s="3" t="inlineStr">
         <is>
           <t>EQ_8_NVDA</t>
         </is>
       </c>
-      <c r="DA2" s="3" t="inlineStr">
+      <c r="DB2" s="3" t="inlineStr">
         <is>
           <t>EQ_12_SPX</t>
         </is>
       </c>
-      <c r="DB2" s="3" t="inlineStr">
+      <c r="DC2" s="3" t="inlineStr">
         <is>
           <t>VEGA_EQ_12_SPX_0.5Y</t>
         </is>
       </c>
-      <c r="DC2" s="3" t="inlineStr">
+      <c r="DD2" s="3" t="inlineStr">
         <is>
           <t>VEGA_EQ_12_SPX_1.0Y</t>
         </is>
       </c>
-      <c r="DD2" s="3" t="inlineStr">
+      <c r="DE2" s="3" t="inlineStr">
         <is>
           <t>VEGA_EQ_12_SPX_3.0Y</t>
         </is>
       </c>
-      <c r="DE2" s="3" t="inlineStr">
+      <c r="DF2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_1.0Y_1.0Y</t>
         </is>
       </c>
-      <c r="DF2" s="3" t="inlineStr">
+      <c r="DG2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_1.0Y_3.0Y</t>
         </is>
       </c>
-      <c r="DG2" s="3" t="inlineStr">
+      <c r="DH2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_3.0Y_0.5Y</t>
         </is>
       </c>
-      <c r="DH2" s="3" t="inlineStr">
+      <c r="DI2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_3.0Y_1.0Y</t>
         </is>
       </c>
-      <c r="DI2" s="3" t="inlineStr">
+      <c r="DJ2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_3.0Y_3.0Y</t>
         </is>
       </c>
-      <c r="DJ2" s="3" t="inlineStr">
+      <c r="DK2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_5.0Y_0.5Y</t>
         </is>
       </c>
-      <c r="DK2" s="3" t="inlineStr">
+      <c r="DL2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_5.0Y_1.0Y</t>
         </is>
       </c>
-      <c r="DL2" s="3" t="inlineStr">
+      <c r="DM2" s="3" t="inlineStr">
         <is>
           <t>VEGA_GIRR_USD_5.0Y_3.0Y</t>
         </is>
       </c>
-      <c r="DM2" s="3" t="inlineStr">
+      <c r="DN2" s="3" t="inlineStr">
         <is>
           <t>CURV_EQ_12_SPX_DN</t>
         </is>
       </c>
-      <c r="DN2" s="3" t="inlineStr">
+      <c r="DO2" s="3" t="inlineStr">
         <is>
           <t>CURV_EQ_12_SPX_UP</t>
         </is>
       </c>
-      <c r="DO2" s="3" t="inlineStr">
+      <c r="DP2" s="3" t="inlineStr">
         <is>
           <t>CURV_GIRR_USD_DN</t>
         </is>
       </c>
-      <c r="DP2" s="3" t="inlineStr">
+      <c r="DQ2" s="3" t="inlineStr">
         <is>
           <t>CURV_GIRR_USD_UP</t>
         </is>
       </c>
-      <c r="DQ2" s="3" t="inlineStr">
+      <c r="DR2" s="3" t="inlineStr">
         <is>
           <t>COMM_2_Brent_Crude_Oil</t>
         </is>
       </c>
-      <c r="DR2" s="3" t="inlineStr">
+      <c r="DS2" s="3" t="inlineStr">
         <is>
           <t>COMM_2_Low_Sulphur_Gas_Oil</t>
         </is>
       </c>
-      <c r="DS2" s="3" t="inlineStr">
+      <c r="DT2" s="3" t="inlineStr">
         <is>
           <t>COMM_2_RBOB_Gasoline</t>
         </is>
       </c>
-      <c r="DT2" s="3" t="inlineStr">
+      <c r="DU2" s="3" t="inlineStr">
         <is>
           <t>COMM_2_ULS_Diesel</t>
         </is>
       </c>
-      <c r="DU2" s="3" t="inlineStr">
+      <c r="DV2" s="3" t="inlineStr">
         <is>
           <t>COMM_2_WTI_Crude_Oil</t>
         </is>
       </c>
-      <c r="DV2" s="3" t="inlineStr">
+      <c r="DW2" s="3" t="inlineStr">
         <is>
           <t>COMM_5_Aluminum</t>
         </is>
       </c>
-      <c r="DW2" s="3" t="inlineStr">
+      <c r="DX2" s="3" t="inlineStr">
         <is>
           <t>COMM_5_Copper</t>
         </is>
       </c>
-      <c r="DX2" s="3" t="inlineStr">
+      <c r="DY2" s="3" t="inlineStr">
         <is>
           <t>COMM_5_Lead</t>
         </is>
       </c>
-      <c r="DY2" s="3" t="inlineStr">
+      <c r="DZ2" s="3" t="inlineStr">
         <is>
           <t>COMM_5_Nickel</t>
         </is>
       </c>
-      <c r="DZ2" s="3" t="inlineStr">
+      <c r="EA2" s="3" t="inlineStr">
         <is>
           <t>COMM_5_Zinc</t>
         </is>
       </c>
-      <c r="EA2" s="3" t="inlineStr">
+      <c r="EB2" s="3" t="inlineStr">
         <is>
           <t>COMM_6_Natural_Gas</t>
         </is>
       </c>
-      <c r="EB2" s="3" t="inlineStr">
+      <c r="EC2" s="3" t="inlineStr">
         <is>
           <t>COMM_7_Gold</t>
         </is>
       </c>
-      <c r="EC2" s="3" t="inlineStr">
+      <c r="ED2" s="3" t="inlineStr">
         <is>
           <t>COMM_7_Silver</t>
         </is>
       </c>
-      <c r="ED2" s="3" t="inlineStr">
+      <c r="EE2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_Corn</t>
         </is>
       </c>
-      <c r="EE2" s="3" t="inlineStr">
+      <c r="EF2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_HRW_Wheat</t>
         </is>
       </c>
-      <c r="EF2" s="3" t="inlineStr">
+      <c r="EG2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_Soybean_Meal</t>
         </is>
       </c>
-      <c r="EG2" s="3" t="inlineStr">
+      <c r="EH2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_Soybean_Oil</t>
         </is>
       </c>
-      <c r="EH2" s="3" t="inlineStr">
+      <c r="EI2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_Soybeans</t>
         </is>
       </c>
-      <c r="EI2" s="3" t="inlineStr">
+      <c r="EJ2" s="3" t="inlineStr">
         <is>
           <t>COMM_8_Wheat</t>
         </is>
       </c>
-      <c r="EJ2" s="3" t="inlineStr">
+      <c r="EK2" s="3" t="inlineStr">
         <is>
           <t>COMM_9_Lean_Hogs</t>
         </is>
       </c>
-      <c r="EK2" s="3" t="inlineStr">
+      <c r="EL2" s="3" t="inlineStr">
         <is>
           <t>COMM_9_Live_Cattle</t>
         </is>
       </c>
-      <c r="EL2" s="3" t="inlineStr">
+      <c r="EM2" s="3" t="inlineStr">
         <is>
           <t>COMM_10_Cocoa</t>
         </is>
       </c>
-      <c r="EM2" s="3" t="inlineStr">
+      <c r="EN2" s="3" t="inlineStr">
         <is>
           <t>COMM_10_Coffee</t>
         </is>
       </c>
-      <c r="EN2" s="3" t="inlineStr">
+      <c r="EO2" s="3" t="inlineStr">
         <is>
           <t>COMM_10_Cotton</t>
         </is>
       </c>
-      <c r="EO2" s="3" t="inlineStr">
+      <c r="EP2" s="3" t="inlineStr">
         <is>
           <t>COMM_10_Sugar</t>
         </is>
       </c>
-      <c r="EP2" s="3" t="inlineStr">
+      <c r="EQ2" s="3" t="inlineStr">
         <is>
           <t>FX_GBP/USD</t>
         </is>
@@ -1476,15 +1482,15 @@
       <c r="AC3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="9" t="n">
+      <c r="AD3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="9" t="n">
         <v>-3758722.560583578</v>
       </c>
-      <c r="AE3" s="9" t="n">
+      <c r="AF3" s="9" t="n">
         <v>-1230166.244988027</v>
       </c>
-      <c r="AF3" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" s="8" t="n">
         <v>0</v>
       </c>
@@ -1825,6 +1831,9 @@
         <v>0</v>
       </c>
       <c r="EP3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ3" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1916,27 +1925,27 @@
       <c r="AA4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="9" t="n">
+      <c r="AB4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9" t="n">
         <v>-10508.36685166701</v>
       </c>
-      <c r="AC4" s="9" t="n">
+      <c r="AD4" s="9" t="n">
         <v>-15589.17307690422</v>
       </c>
-      <c r="AD4" s="9" t="n">
+      <c r="AE4" s="9" t="n">
         <v>-72451.43478698423</v>
       </c>
-      <c r="AE4" s="9" t="n">
+      <c r="AF4" s="9" t="n">
         <v>-161173.1565319019</v>
       </c>
-      <c r="AF4" s="9" t="n">
+      <c r="AG4" s="9" t="n">
         <v>-4574683.000867452</v>
       </c>
-      <c r="AG4" s="9" t="n">
+      <c r="AH4" s="9" t="n">
         <v>-2784562.686628931</v>
       </c>
-      <c r="AH4" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI4" s="8" t="n">
         <v>0</v>
       </c>
@@ -2271,6 +2280,9 @@
         <v>0</v>
       </c>
       <c r="EP4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ4" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2362,21 +2374,21 @@
       <c r="AA5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AB5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9" t="n">
         <v>-3246.661985315313</v>
       </c>
-      <c r="AC5" s="9" t="n">
+      <c r="AD5" s="9" t="n">
         <v>-4877.336995548376</v>
       </c>
-      <c r="AD5" s="9" t="n">
+      <c r="AE5" s="9" t="n">
         <v>-760743.8274098968</v>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AF5" s="9" t="n">
         <v>-247364.7615977938</v>
       </c>
-      <c r="AF5" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" s="8" t="n">
         <v>0</v>
       </c>
@@ -2419,18 +2431,18 @@
       <c r="AT5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" s="9" t="n">
+      <c r="AU5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="9" t="n">
         <v>-8146.620403124416</v>
       </c>
-      <c r="AV5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>-888111.6850874377</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="AX5" s="9" t="n">
         <v>-124200.5980382146</v>
       </c>
-      <c r="AX5" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AY5" s="8" t="n">
         <v>0</v>
       </c>
@@ -2717,6 +2729,9 @@
         <v>0</v>
       </c>
       <c r="EP5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2808,24 +2823,24 @@
       <c r="AA6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AB6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9" t="n">
         <v>-253.5333424589226</v>
       </c>
-      <c r="AC6" s="9" t="n">
+      <c r="AD6" s="9" t="n">
         <v>-6319.914341361255</v>
       </c>
-      <c r="AD6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>-21701.06420493312</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AF6" s="9" t="n">
         <v>-1549357.301580926</v>
       </c>
-      <c r="AF6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
         <v>-38927.48250984823</v>
       </c>
-      <c r="AG6" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH6" s="8" t="n">
         <v>0</v>
       </c>
@@ -2865,18 +2880,18 @@
       <c r="AT6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" s="9" t="n">
+      <c r="AU6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="9" t="n">
         <v>-6594.518198710375</v>
       </c>
-      <c r="AV6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>-799235.8235538858</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AX6" s="9" t="n">
         <v>-816485.7084182699</v>
       </c>
-      <c r="AX6" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AY6" s="8" t="n">
         <v>0</v>
       </c>
@@ -3163,6 +3178,9 @@
         <v>0</v>
       </c>
       <c r="EP6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3254,15 +3272,15 @@
       <c r="AA7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="AB7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9" t="n">
         <v>-170606.3212611184</v>
       </c>
-      <c r="AC7" s="9" t="n">
+      <c r="AD7" s="9" t="n">
         <v>-127955.0664683597</v>
       </c>
-      <c r="AD7" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" s="8" t="n">
         <v>0</v>
       </c>
@@ -3275,12 +3293,12 @@
       <c r="AH7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" s="9" t="n">
+      <c r="AI7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="9" t="n">
         <v>-298852.2357733245</v>
       </c>
-      <c r="AJ7" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AK7" s="8" t="n">
         <v>0</v>
       </c>
@@ -3609,6 +3627,9 @@
         <v>0</v>
       </c>
       <c r="EP7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3700,27 +3721,27 @@
       <c r="AA8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="AB8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9" t="n">
         <v>-7864.240010007961</v>
       </c>
-      <c r="AC8" s="9" t="n">
+      <c r="AD8" s="9" t="n">
         <v>-11896.64808214275</v>
       </c>
-      <c r="AD8" s="9" t="n">
+      <c r="AE8" s="9" t="n">
         <v>-53939.42112402783</v>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AF8" s="9" t="n">
         <v>-119396.8695055219</v>
       </c>
-      <c r="AF8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
         <v>-1841000.945724374</v>
       </c>
-      <c r="AG8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
         <v>-1110483.078573509</v>
       </c>
-      <c r="AH8" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI8" s="8" t="n">
         <v>0</v>
       </c>
@@ -3757,21 +3778,21 @@
       <c r="AT8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" s="9" t="n">
+      <c r="AU8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="9" t="n">
         <v>-19793.25489037365</v>
       </c>
-      <c r="AV8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>-113659.1612174698</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AX8" s="9" t="n">
         <v>-1897688.008100545</v>
       </c>
-      <c r="AX8" s="9" t="n">
+      <c r="AY8" s="9" t="n">
         <v>-1108651.822296053</v>
       </c>
-      <c r="AY8" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ8" s="8" t="n">
         <v>0</v>
       </c>
@@ -4055,6 +4076,9 @@
         <v>0</v>
       </c>
       <c r="EP8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4146,27 +4170,27 @@
       <c r="AA9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" s="9" t="n">
+      <c r="AB9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9" t="n">
         <v>-1740.910802993767</v>
       </c>
-      <c r="AC9" s="9" t="n">
+      <c r="AD9" s="9" t="n">
         <v>-9222.781735672925</v>
       </c>
-      <c r="AD9" s="9" t="n">
+      <c r="AE9" s="9" t="n">
         <v>-32518.26213289633</v>
       </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AF9" s="9" t="n">
         <v>-72348.99589172982</v>
       </c>
-      <c r="AF9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
         <v>-1304036.074720443</v>
       </c>
-      <c r="AG9" s="9" t="n">
+      <c r="AH9" s="9" t="n">
         <v>-2045246.617432156</v>
       </c>
-      <c r="AH9" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI9" s="8" t="n">
         <v>0</v>
       </c>
@@ -4215,21 +4239,21 @@
       <c r="AX9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" s="9" t="n">
+      <c r="AY9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
         <v>-10934.51820565861</v>
       </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="BA9" s="9" t="n">
         <v>-67777.7382895215</v>
       </c>
-      <c r="BA9" s="9" t="n">
+      <c r="BB9" s="9" t="n">
         <v>-1204518.66068413</v>
       </c>
-      <c r="BB9" s="9" t="n">
+      <c r="BC9" s="9" t="n">
         <v>-2077793.972451104</v>
       </c>
-      <c r="BC9" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BD9" s="8" t="n">
         <v>0</v>
       </c>
@@ -4395,39 +4419,39 @@
       <c r="DF9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DG9" s="9" t="n">
+      <c r="DG9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" s="9" t="n">
         <v>-0.2772749203155584</v>
       </c>
-      <c r="DH9" s="9" t="n">
+      <c r="DI9" s="9" t="n">
         <v>-40.23259093778803</v>
       </c>
-      <c r="DI9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" s="9" t="n">
+      <c r="DJ9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" s="9" t="n">
         <v>-0.1181361666351794</v>
       </c>
-      <c r="DK9" s="9" t="n">
+      <c r="DL9" s="9" t="n">
         <v>-17.14155777876474</v>
       </c>
-      <c r="DL9" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DM9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="DN9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DO9" s="9" t="n">
+      <c r="DO9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP9" s="9" t="n">
         <v>827.7520908096703</v>
       </c>
-      <c r="DP9" s="9" t="n">
+      <c r="DQ9" s="9" t="n">
         <v>-3598.884528778297</v>
       </c>
-      <c r="DQ9" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DR9" s="8" t="n">
         <v>0</v>
       </c>
@@ -4501,6 +4525,9 @@
         <v>0</v>
       </c>
       <c r="EP9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4592,21 +4619,21 @@
       <c r="AA10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="AB10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9" t="n">
         <v>-2541.982566413026</v>
       </c>
-      <c r="AC10" s="9" t="n">
+      <c r="AD10" s="9" t="n">
         <v>-7046.908016604903</v>
       </c>
-      <c r="AD10" s="9" t="n">
+      <c r="AE10" s="9" t="n">
         <v>-517503.6028417139</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AF10" s="9" t="n">
         <v>-776267.9640701435</v>
       </c>
-      <c r="AF10" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" s="8" t="n">
         <v>0</v>
       </c>
@@ -4634,18 +4661,18 @@
       <c r="AO10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" s="9" t="n">
+      <c r="AP10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="9" t="n">
         <v>-9614.402937700106</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AR10" s="9" t="n">
         <v>-908617.6549942024</v>
       </c>
-      <c r="AR10" s="9" t="n">
+      <c r="AS10" s="9" t="n">
         <v>-389423.3298912013</v>
       </c>
-      <c r="AS10" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AT10" s="8" t="n">
         <v>0</v>
       </c>
@@ -4947,6 +4974,9 @@
         <v>0</v>
       </c>
       <c r="EP10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5038,27 +5068,27 @@
       <c r="AA11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="9" t="n">
+      <c r="AB11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9" t="n">
         <v>-2025.208861880401</v>
       </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AD11" s="9" t="n">
         <v>-5826.290411448554</v>
       </c>
-      <c r="AD11" s="9" t="n">
+      <c r="AE11" s="9" t="n">
         <v>-387225.4103970931</v>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AF11" s="9" t="n">
         <v>-299792.9285114083</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
         <v>-901953.0329009626</v>
       </c>
-      <c r="AG11" s="9" t="n">
+      <c r="AH11" s="9" t="n">
         <v>-27540.34454517296</v>
       </c>
-      <c r="AH11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI11" s="8" t="n">
         <v>0</v>
       </c>
@@ -5068,21 +5098,21 @@
       <c r="AK11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AL11" s="9" t="n">
+      <c r="AL11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="9" t="n">
         <v>-7836.834188481134</v>
       </c>
-      <c r="AM11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>-412739.3374615167</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AO11" s="9" t="n">
         <v>-1394010.863612664</v>
       </c>
-      <c r="AO11" s="9" t="n">
+      <c r="AP11" s="9" t="n">
         <v>-36604.38258157228</v>
       </c>
-      <c r="AP11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ11" s="8" t="n">
         <v>0</v>
       </c>
@@ -5281,24 +5311,24 @@
       <c r="DD11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DE11" s="9" t="n">
+      <c r="DE11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" s="9" t="n">
         <v>-80.83820524743329</v>
       </c>
-      <c r="DF11" s="9" t="n">
+      <c r="DG11" s="9" t="n">
         <v>-81.05983158121653</v>
       </c>
-      <c r="DG11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH11" s="9" t="n">
+      <c r="DH11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" s="9" t="n">
         <v>-2.716529712948771</v>
       </c>
-      <c r="DI11" s="9" t="n">
+      <c r="DJ11" s="9" t="n">
         <v>-2.723977361236498</v>
       </c>
-      <c r="DJ11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DK11" s="8" t="n">
         <v>0</v>
       </c>
@@ -5311,15 +5341,15 @@
       <c r="DN11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DO11" s="9" t="n">
+      <c r="DO11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" s="9" t="n">
         <v>17352.75349868364</v>
       </c>
-      <c r="DP11" s="9" t="n">
+      <c r="DQ11" s="9" t="n">
         <v>-8996.058506519024</v>
       </c>
-      <c r="DQ11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DR11" s="8" t="n">
         <v>0</v>
       </c>
@@ -5393,6 +5423,9 @@
         <v>0</v>
       </c>
       <c r="EP11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5484,24 +5517,24 @@
       <c r="AA12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB12" s="9" t="n">
+      <c r="AB12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9" t="n">
         <v>-2525.105789061399</v>
       </c>
-      <c r="AC12" s="9" t="n">
+      <c r="AD12" s="9" t="n">
         <v>-8078.170598025736</v>
       </c>
-      <c r="AD12" s="9" t="n">
+      <c r="AE12" s="9" t="n">
         <v>-32088.04338800064</v>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AF12" s="9" t="n">
         <v>-612214.5327810245</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
         <v>-1529175.537621711</v>
       </c>
-      <c r="AG12" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" s="8" t="n">
         <v>0</v>
       </c>
@@ -5514,18 +5547,18 @@
       <c r="AK12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AL12" s="9" t="n">
+      <c r="AL12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="9" t="n">
         <v>-10621.07178654514</v>
       </c>
-      <c r="AM12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>-338337.6452364928</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AO12" s="9" t="n">
         <v>-1835805.912634839</v>
       </c>
-      <c r="AO12" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AP12" s="8" t="n">
         <v>0</v>
       </c>
@@ -5839,6 +5872,9 @@
         <v>0</v>
       </c>
       <c r="EP12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ12" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5930,27 +5966,27 @@
       <c r="AA13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="AB13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9" t="n">
         <v>-2938.413063759526</v>
       </c>
-      <c r="AC13" s="9" t="n">
+      <c r="AD13" s="9" t="n">
         <v>-9192.582691810003</v>
       </c>
-      <c r="AD13" s="9" t="n">
+      <c r="AE13" s="9" t="n">
         <v>-36180.04389983298</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AF13" s="9" t="n">
         <v>-80585.98869587285</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
         <v>-2001407.55134521</v>
       </c>
-      <c r="AG13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
         <v>-620951.8433017251</v>
       </c>
-      <c r="AH13" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI13" s="8" t="n">
         <v>0</v>
       </c>
@@ -5960,21 +5996,21 @@
       <c r="AK13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AL13" s="9" t="n">
+      <c r="AL13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="9" t="n">
         <v>-12065.61451436983</v>
       </c>
-      <c r="AM13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>-74797.50487505044</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AO13" s="9" t="n">
         <v>-1684920.430651175</v>
       </c>
-      <c r="AO13" s="9" t="n">
+      <c r="AP13" s="9" t="n">
         <v>-1093174.646000023</v>
       </c>
-      <c r="AP13" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ13" s="8" t="n">
         <v>0</v>
       </c>
@@ -6182,36 +6218,36 @@
       <c r="DG13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DH13" s="9" t="n">
+      <c r="DH13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" s="9" t="n">
         <v>-100.1575920802016</v>
       </c>
-      <c r="DI13" s="9" t="n">
+      <c r="DJ13" s="9" t="n">
         <v>-32.93039521327227</v>
       </c>
-      <c r="DJ13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK13" s="9" t="n">
+      <c r="DK13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" s="9" t="n">
         <v>-1.425359692915046</v>
       </c>
-      <c r="DL13" s="9" t="n">
+      <c r="DM13" s="9" t="n">
         <v>-0.4686380436460109</v>
       </c>
-      <c r="DM13" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DN13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DO13" s="9" t="n">
+      <c r="DO13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP13" s="9" t="n">
         <v>12925.68844243606</v>
       </c>
-      <c r="DP13" s="9" t="n">
+      <c r="DQ13" s="9" t="n">
         <v>-11828.66290711206</v>
       </c>
-      <c r="DQ13" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DR13" s="8" t="n">
         <v>0</v>
       </c>
@@ -6285,6 +6321,9 @@
         <v>0</v>
       </c>
       <c r="EP13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6376,30 +6415,30 @@
       <c r="AA14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" s="9" t="n">
+      <c r="AB14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="n">
         <v>-2062.823377116274</v>
       </c>
-      <c r="AC14" s="9" t="n">
+      <c r="AD14" s="9" t="n">
         <v>-5680.442748371206</v>
       </c>
-      <c r="AD14" s="9" t="n">
+      <c r="AE14" s="9" t="n">
         <v>-22638.79162444482</v>
       </c>
-      <c r="AE14" s="9" t="n">
+      <c r="AF14" s="9" t="n">
         <v>-49744.51554801362</v>
       </c>
-      <c r="AF14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
         <v>-118321.7105566427</v>
       </c>
-      <c r="AG14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
         <v>-2157134.47180093</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AI14" s="9" t="n">
         <v>-3182916.341691282</v>
       </c>
-      <c r="AI14" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="8" t="n">
         <v>0</v>
       </c>
@@ -6418,24 +6457,24 @@
       <c r="AO14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AP14" s="9" t="n">
+      <c r="AP14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="9" t="n">
         <v>-7764.214905648714</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AR14" s="9" t="n">
         <v>-47674.52966257224</v>
       </c>
-      <c r="AR14" s="9" t="n">
+      <c r="AS14" s="9" t="n">
         <v>-143895.8482423231</v>
       </c>
-      <c r="AS14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
         <v>-2157389.869107646</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AU14" s="9" t="n">
         <v>-3181693.338927004</v>
       </c>
-      <c r="AU14" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" s="8" t="n">
         <v>0</v>
       </c>
@@ -6731,6 +6770,9 @@
         <v>0</v>
       </c>
       <c r="EP14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ14" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6822,18 +6864,18 @@
       <c r="AA15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB15" s="9" t="n">
+      <c r="AB15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9" t="n">
         <v>-1784.460687247247</v>
       </c>
-      <c r="AC15" s="9" t="n">
+      <c r="AD15" s="9" t="n">
         <v>-91934.91256536389</v>
       </c>
-      <c r="AD15" s="9" t="n">
+      <c r="AE15" s="9" t="n">
         <v>-675438.7276953935</v>
       </c>
-      <c r="AE15" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF15" s="8" t="n">
         <v>0</v>
       </c>
@@ -6891,15 +6933,15 @@
       <c r="AX15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" s="9" t="n">
+      <c r="AY15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="9" t="n">
         <v>-94183.114757584</v>
       </c>
-      <c r="AZ15" s="9" t="n">
+      <c r="BA15" s="9" t="n">
         <v>-678865.9661013412</v>
       </c>
-      <c r="BA15" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BB15" s="8" t="n">
         <v>0</v>
       </c>
@@ -7177,6 +7219,9 @@
         <v>0</v>
       </c>
       <c r="EP15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7268,24 +7313,24 @@
       <c r="AA16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="9" t="n">
+      <c r="AB16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9" t="n">
         <v>-1833.855063239298</v>
       </c>
-      <c r="AC16" s="9" t="n">
+      <c r="AD16" s="9" t="n">
         <v>-5258.0431165552</v>
       </c>
-      <c r="AD16" s="9" t="n">
+      <c r="AE16" s="9" t="n">
         <v>-20442.0590009704</v>
       </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AF16" s="9" t="n">
         <v>-418488.9365944855</v>
       </c>
-      <c r="AF16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
         <v>-1748700.578299804</v>
       </c>
-      <c r="AG16" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH16" s="8" t="n">
         <v>0</v>
       </c>
@@ -7325,18 +7370,18 @@
       <c r="AT16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" s="9" t="n">
+      <c r="AU16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="9" t="n">
         <v>-7103.033322778174</v>
       </c>
-      <c r="AV16" s="9" t="n">
+      <c r="AW16" s="9" t="n">
         <v>-229712.2088710921</v>
       </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AX16" s="9" t="n">
         <v>-1957948.808951016</v>
       </c>
-      <c r="AX16" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AY16" s="8" t="n">
         <v>0</v>
       </c>
@@ -7623,6 +7668,9 @@
         <v>0</v>
       </c>
       <c r="EP16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7714,27 +7762,27 @@
       <c r="AA17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="9" t="n">
+      <c r="AB17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9" t="n">
         <v>-1595.840181835229</v>
       </c>
-      <c r="AC17" s="9" t="n">
+      <c r="AD17" s="9" t="n">
         <v>-8513.651531302457</v>
       </c>
-      <c r="AD17" s="9" t="n">
+      <c r="AE17" s="9" t="n">
         <v>-32266.56449595566</v>
       </c>
-      <c r="AE17" s="9" t="n">
+      <c r="AF17" s="9" t="n">
         <v>-70719.80224321806</v>
       </c>
-      <c r="AF17" s="9" t="n">
+      <c r="AG17" s="9" t="n">
         <v>-2044653.197763637</v>
       </c>
-      <c r="AG17" s="9" t="n">
+      <c r="AH17" s="9" t="n">
         <v>-580553.0642896884</v>
       </c>
-      <c r="AH17" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI17" s="8" t="n">
         <v>0</v>
       </c>
@@ -7771,21 +7819,21 @@
       <c r="AT17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" s="9" t="n">
+      <c r="AU17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="9" t="n">
         <v>-10123.95090299378</v>
       </c>
-      <c r="AV17" s="9" t="n">
+      <c r="AW17" s="9" t="n">
         <v>-67617.44843026917</v>
       </c>
-      <c r="AW17" s="9" t="n">
+      <c r="AX17" s="9" t="n">
         <v>-2078143.837311302</v>
       </c>
-      <c r="AX17" s="9" t="n">
+      <c r="AY17" s="9" t="n">
         <v>-580033.5285115351</v>
       </c>
-      <c r="AY17" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ17" s="8" t="n">
         <v>0</v>
       </c>
@@ -8069,6 +8117,9 @@
         <v>0</v>
       </c>
       <c r="EP17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ17" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8160,27 +8211,27 @@
       <c r="AA18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AB18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="9" t="n">
         <v>-2474.05933743039</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AD18" s="9" t="n">
         <v>-7288.518560869761</v>
       </c>
-      <c r="AD18" s="9" t="n">
+      <c r="AE18" s="9" t="n">
         <v>-27370.64637000231</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AF18" s="9" t="n">
         <v>-60267.58213380389</v>
       </c>
-      <c r="AF18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
         <v>-699684.8823121126</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AH18" s="9" t="n">
         <v>-2751351.934562479</v>
       </c>
-      <c r="AH18" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI18" s="8" t="n">
         <v>0</v>
       </c>
@@ -8202,21 +8253,21 @@
       <c r="AO18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AP18" s="9" t="n">
+      <c r="AP18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="9" t="n">
         <v>-9781.753516278968</v>
       </c>
-      <c r="AQ18" s="9" t="n">
+      <c r="AR18" s="9" t="n">
         <v>-57604.98026660343</v>
       </c>
-      <c r="AR18" s="9" t="n">
+      <c r="AS18" s="9" t="n">
         <v>-731293.377132772</v>
       </c>
-      <c r="AS18" s="9" t="n">
+      <c r="AT18" s="9" t="n">
         <v>-2756783.550043451</v>
       </c>
-      <c r="AT18" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AU18" s="8" t="n">
         <v>0</v>
       </c>
@@ -8515,6 +8566,9 @@
         <v>0</v>
       </c>
       <c r="EP18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ18" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8606,18 +8660,18 @@
       <c r="AA19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" s="9" t="n">
+      <c r="AB19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="9" t="n">
         <v>-3115.672679768977</v>
       </c>
-      <c r="AC19" s="9" t="n">
+      <c r="AD19" s="9" t="n">
         <v>-316080.8010226219</v>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AE19" s="9" t="n">
         <v>-292791.0509672529</v>
       </c>
-      <c r="AE19" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF19" s="8" t="n">
         <v>0</v>
       </c>
@@ -8627,15 +8681,15 @@
       <c r="AH19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="9" t="n">
+      <c r="AI19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="9" t="n">
         <v>-319718.2253641699</v>
       </c>
-      <c r="AJ19" s="9" t="n">
+      <c r="AK19" s="9" t="n">
         <v>-293272.2599865088</v>
       </c>
-      <c r="AK19" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AL19" s="8" t="n">
         <v>0</v>
       </c>
@@ -8961,6 +9015,9 @@
         <v>0</v>
       </c>
       <c r="EP19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ19" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9052,21 +9109,21 @@
       <c r="AA20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" s="9" t="n">
+      <c r="AB20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="9" t="n">
         <v>-3623.861249650417</v>
       </c>
-      <c r="AC20" s="9" t="n">
+      <c r="AD20" s="9" t="n">
         <v>-8021.245380803066</v>
       </c>
-      <c r="AD20" s="9" t="n">
+      <c r="AE20" s="9" t="n">
         <v>-788278.5087248862</v>
       </c>
-      <c r="AE20" s="9" t="n">
+      <c r="AF20" s="9" t="n">
         <v>-182602.5599186209</v>
       </c>
-      <c r="AF20" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" s="8" t="n">
         <v>0</v>
       </c>
@@ -9082,18 +9139,18 @@
       <c r="AK20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AL20" s="9" t="n">
+      <c r="AL20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="9" t="n">
         <v>-11675.19570122977</v>
       </c>
-      <c r="AM20" s="9" t="n">
+      <c r="AN20" s="9" t="n">
         <v>-882946.3373887733</v>
       </c>
-      <c r="AN20" s="9" t="n">
+      <c r="AO20" s="9" t="n">
         <v>-91652.40458833068</v>
       </c>
-      <c r="AO20" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AP20" s="8" t="n">
         <v>0</v>
       </c>
@@ -9407,6 +9464,9 @@
         <v>0</v>
       </c>
       <c r="EP20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9498,27 +9558,27 @@
       <c r="AA21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" s="9" t="n">
+      <c r="AB21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9" t="n">
         <v>-7450.253467936818</v>
       </c>
-      <c r="AC21" s="9" t="n">
+      <c r="AD21" s="9" t="n">
         <v>-12176.51527383623</v>
       </c>
-      <c r="AD21" s="9" t="n">
+      <c r="AE21" s="9" t="n">
         <v>-54177.75124561785</v>
       </c>
-      <c r="AE21" s="9" t="n">
+      <c r="AF21" s="9" t="n">
         <v>-119232.1289586857</v>
       </c>
-      <c r="AF21" s="9" t="n">
+      <c r="AG21" s="9" t="n">
         <v>-2173695.844803774</v>
       </c>
-      <c r="AG21" s="9" t="n">
+      <c r="AH21" s="9" t="n">
         <v>-397255.108594436</v>
       </c>
-      <c r="AH21" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI21" s="8" t="n">
         <v>0</v>
       </c>
@@ -9555,21 +9615,21 @@
       <c r="AT21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" s="9" t="n">
+      <c r="AU21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="9" t="n">
         <v>-19662.25261753607</v>
       </c>
-      <c r="AV21" s="9" t="n">
+      <c r="AW21" s="9" t="n">
         <v>-113873.4170310727</v>
       </c>
-      <c r="AW21" s="9" t="n">
+      <c r="AX21" s="9" t="n">
         <v>-2233290.285596808</v>
       </c>
-      <c r="AX21" s="9" t="n">
+      <c r="AY21" s="9" t="n">
         <v>-397260.1684438927</v>
       </c>
-      <c r="AY21" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ21" s="8" t="n">
         <v>0</v>
       </c>
@@ -9853,6 +9913,9 @@
         <v>0</v>
       </c>
       <c r="EP21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9944,39 +10007,39 @@
       <c r="AA22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB22" s="9" t="n">
+      <c r="AB22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="9" t="n">
         <v>-3303.474141318929</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AD22" s="9" t="n">
         <v>-4879.389729808281</v>
       </c>
-      <c r="AD22" s="9" t="n">
+      <c r="AE22" s="9" t="n">
         <v>-22569.55533158589</v>
       </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AF22" s="9" t="n">
         <v>-1297033.264748904</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AG22" s="9" t="n">
         <v>-481177.5406961942</v>
       </c>
-      <c r="AG22" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="9" t="n">
+      <c r="AI22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="9" t="n">
         <v>-8201.69967636275</v>
       </c>
-      <c r="AJ22" s="9" t="n">
+      <c r="AK22" s="9" t="n">
         <v>-672275.7134144786</v>
       </c>
-      <c r="AK22" s="9" t="n">
+      <c r="AL22" s="9" t="n">
         <v>-1131584.479480352</v>
       </c>
-      <c r="AL22" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AM22" s="8" t="n">
         <v>0</v>
       </c>
@@ -10299,6 +10362,9 @@
         <v>0</v>
       </c>
       <c r="EP22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10390,21 +10456,21 @@
       <c r="AA23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" s="9" t="n">
+      <c r="AB23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="9" t="n">
         <v>-1105.908805982381</v>
       </c>
-      <c r="AC23" s="9" t="n">
+      <c r="AD23" s="9" t="n">
         <v>-5831.637950223012</v>
       </c>
-      <c r="AD23" s="9" t="n">
+      <c r="AE23" s="9" t="n">
         <v>-524961.4898602318</v>
       </c>
-      <c r="AE23" s="9" t="n">
+      <c r="AF23" s="9" t="n">
         <v>-751876.8596991663</v>
       </c>
-      <c r="AF23" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG23" s="8" t="n">
         <v>0</v>
       </c>
@@ -10459,18 +10525,18 @@
       <c r="AX23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" s="9" t="n">
+      <c r="AY23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="9" t="n">
         <v>-6949.400519658866</v>
       </c>
-      <c r="AZ23" s="9" t="n">
+      <c r="BA23" s="9" t="n">
         <v>-901888.8530566755</v>
       </c>
-      <c r="BA23" s="9" t="n">
+      <c r="BB23" s="9" t="n">
         <v>-376359.9717905208</v>
       </c>
-      <c r="BB23" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BC23" s="8" t="n">
         <v>0</v>
       </c>
@@ -10745,6 +10811,9 @@
         <v>0</v>
       </c>
       <c r="EP23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ23" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10836,27 +10905,27 @@
       <c r="AA24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB24" s="9" t="n">
+      <c r="AB24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="9" t="n">
         <v>-838.740302469887</v>
       </c>
-      <c r="AC24" s="9" t="n">
+      <c r="AD24" s="9" t="n">
         <v>-5936.84353577828</v>
       </c>
-      <c r="AD24" s="9" t="n">
+      <c r="AE24" s="9" t="n">
         <v>-20441.33173563978</v>
       </c>
-      <c r="AE24" s="9" t="n">
+      <c r="AF24" s="9" t="n">
         <v>-45209.35725162189</v>
       </c>
-      <c r="AF24" s="9" t="n">
+      <c r="AG24" s="9" t="n">
         <v>-1434479.546360024</v>
       </c>
-      <c r="AG24" s="9" t="n">
+      <c r="AH24" s="9" t="n">
         <v>-1564632.039232379</v>
       </c>
-      <c r="AH24" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI24" s="8" t="n">
         <v>0</v>
       </c>
@@ -10866,21 +10935,21 @@
       <c r="AK24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AL24" s="9" t="n">
+      <c r="AL24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="9" t="n">
         <v>-6785.789476055015</v>
       </c>
-      <c r="AM24" s="9" t="n">
+      <c r="AN24" s="9" t="n">
         <v>-43054.64278201043</v>
       </c>
-      <c r="AN24" s="9" t="n">
+      <c r="AO24" s="9" t="n">
         <v>-1455530.530647422</v>
       </c>
-      <c r="AO24" s="9" t="n">
+      <c r="AP24" s="9" t="n">
         <v>-1562899.242201865</v>
       </c>
-      <c r="AP24" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ24" s="8" t="n">
         <v>0</v>
       </c>
@@ -11191,6 +11260,9 @@
         <v>0</v>
       </c>
       <c r="EP24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11510,12 +11582,12 @@
       <c r="CY25" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CZ25" s="9" t="n">
+      <c r="CZ25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA25" s="9" t="n">
         <v>4902017.6</v>
       </c>
-      <c r="DA25" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DB25" s="8" t="n">
         <v>0</v>
       </c>
@@ -11637,6 +11709,9 @@
         <v>0</v>
       </c>
       <c r="EP25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ25" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11935,12 +12010,12 @@
       <c r="CR26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CS26" s="9" t="n">
+      <c r="CS26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT26" s="9" t="n">
         <v>3696642.18</v>
       </c>
-      <c r="CT26" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CU26" s="8" t="n">
         <v>0</v>
       </c>
@@ -12083,6 +12158,9 @@
         <v>0</v>
       </c>
       <c r="EP26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ26" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12390,12 +12468,12 @@
       <c r="CU27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CV27" s="9" t="n">
+      <c r="CV27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW27" s="9" t="n">
         <v>3601681.25</v>
       </c>
-      <c r="CW27" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CX27" s="8" t="n">
         <v>0</v>
       </c>
@@ -12529,6 +12607,9 @@
         <v>0</v>
       </c>
       <c r="EP27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12845,12 +12926,12 @@
       <c r="CX28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CY28" s="9" t="n">
+      <c r="CY28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ28" s="9" t="n">
         <v>3599718.48</v>
       </c>
-      <c r="CZ28" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DA28" s="8" t="n">
         <v>0</v>
       </c>
@@ -12975,6 +13056,9 @@
         <v>0</v>
       </c>
       <c r="EP28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13267,12 +13351,12 @@
       <c r="CP29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CQ29" s="9" t="n">
+      <c r="CQ29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR29" s="9" t="n">
         <v>2580754.41</v>
       </c>
-      <c r="CR29" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CS29" s="8" t="n">
         <v>0</v>
       </c>
@@ -13421,6 +13505,9 @@
         <v>0</v>
       </c>
       <c r="EP29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ29" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13734,12 +13821,12 @@
       <c r="CW30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CX30" s="9" t="n">
+      <c r="CX30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY30" s="9" t="n">
         <v>1993874.75</v>
       </c>
-      <c r="CY30" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CZ30" s="8" t="n">
         <v>0</v>
       </c>
@@ -13867,6 +13954,9 @@
         <v>0</v>
       </c>
       <c r="EP30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ30" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14177,12 +14267,12 @@
       <c r="CV31" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CW31" s="9" t="n">
+      <c r="CW31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX31" s="9" t="n">
         <v>1128362.08</v>
       </c>
-      <c r="CX31" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CY31" s="8" t="n">
         <v>0</v>
       </c>
@@ -14313,6 +14403,9 @@
         <v>0</v>
       </c>
       <c r="EP31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ31" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14614,12 +14707,12 @@
       <c r="CS32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CT32" s="9" t="n">
+      <c r="CT32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU32" s="9" t="n">
         <v>656064.78</v>
       </c>
-      <c r="CU32" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CV32" s="8" t="n">
         <v>0</v>
       </c>
@@ -14759,6 +14852,9 @@
         <v>0</v>
       </c>
       <c r="EP32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ32" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15054,12 +15150,12 @@
       <c r="CQ33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CR33" s="9" t="n">
+      <c r="CR33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS33" s="9" t="n">
         <v>567812.96</v>
       </c>
-      <c r="CS33" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CT33" s="8" t="n">
         <v>0</v>
       </c>
@@ -15205,6 +15301,9 @@
         <v>0</v>
       </c>
       <c r="EP33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ33" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15509,12 +15608,12 @@
       <c r="CT34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CU34" s="9" t="n">
+      <c r="CU34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV34" s="9" t="n">
         <v>522491.32</v>
       </c>
-      <c r="CV34" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CW34" s="8" t="n">
         <v>0</v>
       </c>
@@ -15651,6 +15750,9 @@
         <v>0</v>
       </c>
       <c r="EP34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ34" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15973,15 +16075,15 @@
       <c r="CZ35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DA35" s="9" t="n">
+      <c r="DA35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB35" s="9" t="n">
         <v>-1299.704282375784</v>
       </c>
-      <c r="DB35" s="9" t="n">
+      <c r="DC35" s="9" t="n">
         <v>-776111.8153708656</v>
       </c>
-      <c r="DC35" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DD35" s="8" t="n">
         <v>0</v>
       </c>
@@ -16009,15 +16111,15 @@
       <c r="DL35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DM35" s="9" t="n">
+      <c r="DM35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN35" s="9" t="n">
         <v>-13113.74135703345</v>
       </c>
-      <c r="DN35" s="9" t="n">
+      <c r="DO35" s="9" t="n">
         <v>13390.73854265853</v>
       </c>
-      <c r="DO35" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DP35" s="8" t="n">
         <v>0</v>
       </c>
@@ -16097,6 +16199,9 @@
         <v>0</v>
       </c>
       <c r="EP35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ35" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16419,21 +16524,21 @@
       <c r="CZ36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DA36" s="9" t="n">
+      <c r="DA36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB36" s="9" t="n">
         <v>-1940.475460247293</v>
       </c>
-      <c r="DB36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC36" s="9" t="n">
+      <c r="DC36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD36" s="9" t="n">
         <v>-2004105.853480715</v>
       </c>
-      <c r="DD36" s="9" t="n">
+      <c r="DE36" s="9" t="n">
         <v>-146462.3815066698</v>
       </c>
-      <c r="DE36" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DF36" s="8" t="n">
         <v>0</v>
       </c>
@@ -16455,15 +16560,15 @@
       <c r="DL36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DM36" s="9" t="n">
+      <c r="DM36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN36" s="9" t="n">
         <v>-19725.50163030073</v>
       </c>
-      <c r="DN36" s="9" t="n">
+      <c r="DO36" s="9" t="n">
         <v>19845.00800154645</v>
       </c>
-      <c r="DO36" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DP36" s="8" t="n">
         <v>0</v>
       </c>
@@ -16543,6 +16648,9 @@
         <v>0</v>
       </c>
       <c r="EP36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ36" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16865,15 +16973,15 @@
       <c r="CZ37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DA37" s="9" t="n">
+      <c r="DA37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB37" s="9" t="n">
         <v>-848.6106865621699</v>
       </c>
-      <c r="DB37" s="9" t="n">
+      <c r="DC37" s="9" t="n">
         <v>-492341.2705299766</v>
       </c>
-      <c r="DC37" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DD37" s="8" t="n">
         <v>0</v>
       </c>
@@ -16901,15 +17009,15 @@
       <c r="DL37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DM37" s="9" t="n">
+      <c r="DM37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN37" s="9" t="n">
         <v>-8511.471466746127</v>
       </c>
-      <c r="DN37" s="9" t="n">
+      <c r="DO37" s="9" t="n">
         <v>8795.23765605607</v>
       </c>
-      <c r="DO37" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DP37" s="8" t="n">
         <v>0</v>
       </c>
@@ -16989,6 +17097,9 @@
         <v>0</v>
       </c>
       <c r="EP37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ37" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17311,15 +17422,15 @@
       <c r="CZ38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DA38" s="9" t="n">
+      <c r="DA38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB38" s="9" t="n">
         <v>-1146.661653509631</v>
       </c>
-      <c r="DB38" s="9" t="n">
+      <c r="DC38" s="9" t="n">
         <v>-643003.4204496703</v>
       </c>
-      <c r="DC38" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DD38" s="8" t="n">
         <v>0</v>
       </c>
@@ -17347,15 +17458,15 @@
       <c r="DL38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DM38" s="9" t="n">
+      <c r="DM38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN38" s="9" t="n">
         <v>-11542.29826021151</v>
       </c>
-      <c r="DN38" s="9" t="n">
+      <c r="DO38" s="9" t="n">
         <v>11841.71588674535</v>
       </c>
-      <c r="DO38" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="DP38" s="8" t="n">
         <v>0</v>
       </c>
@@ -17435,6 +17546,9 @@
         <v>0</v>
       </c>
       <c r="EP38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ38" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17526,24 +17640,24 @@
       <c r="AA39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB39" s="9" t="n">
+      <c r="AB39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="9" t="n">
         <v>-357702.4803310633</v>
       </c>
-      <c r="AC39" s="9" t="n">
+      <c r="AD39" s="9" t="n">
         <v>-960840.3903990984</v>
       </c>
-      <c r="AD39" s="9" t="n">
+      <c r="AE39" s="9" t="n">
         <v>-3579931.614771485</v>
       </c>
-      <c r="AE39" s="9" t="n">
+      <c r="AF39" s="9" t="n">
         <v>-15203467.17365086</v>
       </c>
-      <c r="AF39" s="9" t="n">
+      <c r="AG39" s="9" t="n">
         <v>-74213821.4956224</v>
       </c>
-      <c r="AG39" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH39" s="8" t="n">
         <v>0</v>
       </c>
@@ -17607,18 +17721,18 @@
       <c r="BB39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" s="9" t="n">
+      <c r="BC39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" s="9" t="n">
         <v>-1104389.242455363</v>
       </c>
-      <c r="BD39" s="9" t="n">
+      <c r="BE39" s="9" t="n">
         <v>-11181740.66208303</v>
       </c>
-      <c r="BE39" s="9" t="n">
+      <c r="BF39" s="9" t="n">
         <v>-81814499.41888452</v>
       </c>
-      <c r="BF39" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BG39" s="8" t="n">
         <v>0</v>
       </c>
@@ -17881,6 +17995,9 @@
         <v>0</v>
       </c>
       <c r="EP39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ39" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17972,24 +18089,24 @@
       <c r="AA40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB40" s="9" t="n">
+      <c r="AB40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="9" t="n">
         <v>-106776.9982665777</v>
       </c>
-      <c r="AC40" s="9" t="n">
+      <c r="AD40" s="9" t="n">
         <v>-284896.4896798134</v>
       </c>
-      <c r="AD40" s="9" t="n">
+      <c r="AE40" s="9" t="n">
         <v>-1048025.121316314</v>
       </c>
-      <c r="AE40" s="9" t="n">
+      <c r="AF40" s="9" t="n">
         <v>-4329605.248291045</v>
       </c>
-      <c r="AF40" s="9" t="n">
+      <c r="AG40" s="9" t="n">
         <v>-20946648.05917069</v>
       </c>
-      <c r="AG40" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH40" s="8" t="n">
         <v>0</v>
       </c>
@@ -18113,18 +18230,18 @@
       <c r="BV40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BW40" s="9" t="n">
+      <c r="BW40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" s="9" t="n">
         <v>-327722.5342579186</v>
       </c>
-      <c r="BX40" s="9" t="n">
+      <c r="BY40" s="9" t="n">
         <v>-3212849.030438811</v>
       </c>
-      <c r="BY40" s="9" t="n">
+      <c r="BZ40" s="9" t="n">
         <v>-23111153.02942693</v>
       </c>
-      <c r="BZ40" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CA40" s="8" t="n">
         <v>0</v>
       </c>
@@ -18327,6 +18444,9 @@
         <v>0</v>
       </c>
       <c r="EP40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ40" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18418,24 +18538,24 @@
       <c r="AA41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB41" s="9" t="n">
+      <c r="AB41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="9" t="n">
         <v>35592.33276173472</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AD41" s="9" t="n">
         <v>94965.49656614661</v>
       </c>
-      <c r="AD41" s="9" t="n">
+      <c r="AE41" s="9" t="n">
         <v>349341.7071131989</v>
       </c>
-      <c r="AE41" s="9" t="n">
+      <c r="AF41" s="9" t="n">
         <v>1443201.749436557</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AG41" s="9" t="n">
         <v>6982216.019723564</v>
       </c>
-      <c r="AG41" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH41" s="8" t="n">
         <v>0</v>
       </c>
@@ -18559,18 +18679,18 @@
       <c r="BV41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BW41" s="9" t="n">
+      <c r="BW41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" s="9" t="n">
         <v>109240.8447572961</v>
       </c>
-      <c r="BX41" s="9" t="n">
+      <c r="BY41" s="9" t="n">
         <v>1070949.676814489</v>
       </c>
-      <c r="BY41" s="9" t="n">
+      <c r="BZ41" s="9" t="n">
         <v>7703717.676475644</v>
       </c>
-      <c r="BZ41" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CA41" s="8" t="n">
         <v>0</v>
       </c>
@@ -18773,6 +18893,9 @@
         <v>0</v>
       </c>
       <c r="EP41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ41" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18864,30 +18987,30 @@
       <c r="AA42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB42" s="9" t="n">
+      <c r="AB42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9" t="n">
         <v>-297614.8560643196</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AD42" s="9" t="n">
         <v>-836184.7604811192</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AE42" s="9" t="n">
         <v>-3232412.927746773</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AF42" s="9" t="n">
         <v>-7097298.936247826</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AG42" s="9" t="n">
         <v>-16569641.40117168</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AH42" s="9" t="n">
         <v>-224373919.0888405</v>
       </c>
-      <c r="AH42" s="9" t="n">
+      <c r="AI42" s="9" t="n">
         <v>-384148289.9138331</v>
       </c>
-      <c r="AI42" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ42" s="8" t="n">
         <v>0</v>
       </c>
@@ -18954,24 +19077,24 @@
       <c r="BE42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BF42" s="9" t="n">
+      <c r="BF42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" s="9" t="n">
         <v>-955700.3554701805</v>
       </c>
-      <c r="BG42" s="9" t="n">
+      <c r="BH42" s="9" t="n">
         <v>-6781109.845489264</v>
       </c>
-      <c r="BH42" s="9" t="n">
+      <c r="BI42" s="9" t="n">
         <v>-20118222.52333164</v>
       </c>
-      <c r="BI42" s="9" t="n">
+      <c r="BJ42" s="9" t="n">
         <v>-224373919.0888405</v>
       </c>
-      <c r="BJ42" s="9" t="n">
+      <c r="BK42" s="9" t="n">
         <v>-384148289.9139822</v>
       </c>
-      <c r="BK42" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BL42" s="8" t="n">
         <v>0</v>
       </c>
@@ -19219,6 +19342,9 @@
         <v>0</v>
       </c>
       <c r="EP42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ42" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19310,30 +19436,30 @@
       <c r="AA43" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB43" s="9" t="n">
+      <c r="AB43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="9" t="n">
         <v>-23763.62897455692</v>
       </c>
-      <c r="AC43" s="9" t="n">
+      <c r="AD43" s="9" t="n">
         <v>-66595.87878733873</v>
       </c>
-      <c r="AD43" s="9" t="n">
+      <c r="AE43" s="9" t="n">
         <v>-256176.1578638107</v>
       </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AF43" s="9" t="n">
         <v>-558646.9296645373</v>
       </c>
-      <c r="AF43" s="9" t="n">
+      <c r="AG43" s="9" t="n">
         <v>-1288560.424018651</v>
       </c>
-      <c r="AG43" s="9" t="n">
+      <c r="AH43" s="9" t="n">
         <v>-16704108.94773901</v>
       </c>
-      <c r="AH43" s="9" t="n">
+      <c r="AI43" s="9" t="n">
         <v>-28445049.33927208</v>
       </c>
-      <c r="AI43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ43" s="8" t="n">
         <v>0</v>
       </c>
@@ -19400,24 +19526,24 @@
       <c r="BE43" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BF43" s="9" t="n">
+      <c r="BF43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" s="9" t="n">
         <v>-76136.68670877814</v>
       </c>
-      <c r="BG43" s="9" t="n">
+      <c r="BH43" s="9" t="n">
         <v>-535503.3325683326</v>
       </c>
-      <c r="BH43" s="9" t="n">
+      <c r="BI43" s="9" t="n">
         <v>-1567878.566635773</v>
       </c>
-      <c r="BI43" s="9" t="n">
+      <c r="BJ43" s="9" t="n">
         <v>-16704108.94773901</v>
       </c>
-      <c r="BJ43" s="9" t="n">
+      <c r="BK43" s="9" t="n">
         <v>-28445049.33927208</v>
       </c>
-      <c r="BK43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BL43" s="8" t="n">
         <v>0</v>
       </c>
@@ -19665,6 +19791,9 @@
         <v>0</v>
       </c>
       <c r="EP43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ43" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19756,30 +19885,30 @@
       <c r="AA44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB44" s="9" t="n">
+      <c r="AB44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="9" t="n">
         <v>-44406.42671659589</v>
       </c>
-      <c r="AC44" s="9" t="n">
+      <c r="AD44" s="9" t="n">
         <v>-123883.8386535645</v>
       </c>
-      <c r="AD44" s="9" t="n">
+      <c r="AE44" s="9" t="n">
         <v>-472430.1412142813</v>
       </c>
-      <c r="AE44" s="9" t="n">
+      <c r="AF44" s="9" t="n">
         <v>-1017860.648129135</v>
       </c>
-      <c r="AF44" s="9" t="n">
+      <c r="AG44" s="9" t="n">
         <v>-2298152.830861509</v>
       </c>
-      <c r="AG44" s="9" t="n">
+      <c r="AH44" s="9" t="n">
         <v>-27587439.55500424</v>
       </c>
-      <c r="AH44" s="9" t="n">
+      <c r="AI44" s="9" t="n">
         <v>-46515278.08142826</v>
       </c>
-      <c r="AI44" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ44" s="8" t="n">
         <v>0</v>
       </c>
@@ -19906,24 +20035,24 @@
       <c r="BY44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BZ44" s="9" t="n">
+      <c r="BZ44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA44" s="9" t="n">
         <v>-141705.4025270045</v>
       </c>
-      <c r="CA44" s="9" t="n">
+      <c r="CB44" s="9" t="n">
         <v>-981367.1435788274</v>
       </c>
-      <c r="CB44" s="9" t="n">
+      <c r="CC44" s="9" t="n">
         <v>-2807073.642592877</v>
       </c>
-      <c r="CC44" s="9" t="n">
+      <c r="CD44" s="9" t="n">
         <v>-27587439.55498561</v>
       </c>
-      <c r="CD44" s="9" t="n">
+      <c r="CE44" s="9" t="n">
         <v>-46515278.08142826</v>
       </c>
-      <c r="CE44" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CF44" s="8" t="n">
         <v>0</v>
       </c>
@@ -20111,6 +20240,9 @@
         <v>0</v>
       </c>
       <c r="EP44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ44" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20202,27 +20334,27 @@
       <c r="AA45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB45" s="9" t="n">
+      <c r="AB45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="9" t="n">
         <v>-2747809.217870235</v>
       </c>
-      <c r="AC45" s="9" t="n">
+      <c r="AD45" s="9" t="n">
         <v>-7847564.217448235</v>
       </c>
-      <c r="AD45" s="9" t="n">
+      <c r="AE45" s="9" t="n">
         <v>-29930864.91882801</v>
       </c>
-      <c r="AE45" s="9" t="n">
+      <c r="AF45" s="9" t="n">
         <v>-63813410.87520123</v>
       </c>
-      <c r="AF45" s="9" t="n">
+      <c r="AG45" s="9" t="n">
         <v>-141810473.7871885</v>
       </c>
-      <c r="AG45" s="9" t="n">
+      <c r="AH45" s="9" t="n">
         <v>-91689947.71838188</v>
       </c>
-      <c r="AH45" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI45" s="8" t="n">
         <v>0</v>
       </c>
@@ -20331,21 +20463,21 @@
       <c r="BR45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BS45" s="9" t="n">
+      <c r="BS45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT45" s="9" t="n">
         <v>-9007085.128128529</v>
       </c>
-      <c r="BT45" s="9" t="n">
+      <c r="BU45" s="9" t="n">
         <v>-61838026.80522203</v>
       </c>
-      <c r="BU45" s="9" t="n">
+      <c r="BV45" s="9" t="n">
         <v>-173716648.9610076</v>
       </c>
-      <c r="BV45" s="9" t="n">
+      <c r="BW45" s="9" t="n">
         <v>-91689947.71838188</v>
       </c>
-      <c r="BW45" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BX45" s="8" t="n">
         <v>0</v>
       </c>
@@ -20557,6 +20689,9 @@
         <v>0</v>
       </c>
       <c r="EP45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ45" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20648,27 +20783,27 @@
       <c r="AA46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB46" s="9" t="n">
+      <c r="AB46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="9" t="n">
         <v>-127647.4183797836</v>
       </c>
-      <c r="AC46" s="9" t="n">
+      <c r="AD46" s="9" t="n">
         <v>-372421.0401624441</v>
       </c>
-      <c r="AD46" s="9" t="n">
+      <c r="AE46" s="9" t="n">
         <v>-1440923.745781183</v>
       </c>
-      <c r="AE46" s="9" t="n">
+      <c r="AF46" s="9" t="n">
         <v>-7319799.683764577</v>
       </c>
-      <c r="AF46" s="9" t="n">
+      <c r="AG46" s="9" t="n">
         <v>-79992683.81267786</v>
       </c>
-      <c r="AG46" s="9" t="n">
+      <c r="AH46" s="9" t="n">
         <v>-55745407.37092495</v>
       </c>
-      <c r="AH46" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI46" s="8" t="n">
         <v>0</v>
       </c>
@@ -20837,21 +20972,21 @@
       <c r="CL46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CM46" s="9" t="n">
+      <c r="CM46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN46" s="9" t="n">
         <v>-426343.5088843107</v>
       </c>
-      <c r="CN46" s="9" t="n">
+      <c r="CO46" s="9" t="n">
         <v>-5100884.117037058</v>
       </c>
-      <c r="CO46" s="9" t="n">
+      <c r="CP46" s="9" t="n">
         <v>-83652175.07608235</v>
       </c>
-      <c r="CP46" s="9" t="n">
+      <c r="CQ46" s="9" t="n">
         <v>-55745407.37092495</v>
       </c>
-      <c r="CQ46" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CR46" s="8" t="n">
         <v>0</v>
       </c>
@@ -21003,6 +21138,9 @@
         <v>0</v>
       </c>
       <c r="EP46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ46" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21094,27 +21232,27 @@
       <c r="AA47" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB47" s="9" t="n">
+      <c r="AB47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="9" t="n">
         <v>-56732.18593001366</v>
       </c>
-      <c r="AC47" s="9" t="n">
+      <c r="AD47" s="9" t="n">
         <v>-165520.4623192549</v>
       </c>
-      <c r="AD47" s="9" t="n">
+      <c r="AE47" s="9" t="n">
         <v>-640410.5537012219</v>
       </c>
-      <c r="AE47" s="9" t="n">
+      <c r="AF47" s="9" t="n">
         <v>-3253244.303911924</v>
       </c>
-      <c r="AF47" s="9" t="n">
+      <c r="AG47" s="9" t="n">
         <v>-35552303.91677469</v>
       </c>
-      <c r="AG47" s="9" t="n">
+      <c r="AH47" s="9" t="n">
         <v>-24775736.60936207</v>
       </c>
-      <c r="AH47" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI47" s="8" t="n">
         <v>0</v>
       </c>
@@ -21283,21 +21421,21 @@
       <c r="CL47" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CM47" s="9" t="n">
+      <c r="CM47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN47" s="9" t="n">
         <v>-189486.0039651394</v>
       </c>
-      <c r="CN47" s="9" t="n">
+      <c r="CO47" s="9" t="n">
         <v>-2267059.607580304</v>
       </c>
-      <c r="CO47" s="9" t="n">
+      <c r="CP47" s="9" t="n">
         <v>-37178744.47830021</v>
       </c>
-      <c r="CP47" s="9" t="n">
+      <c r="CQ47" s="9" t="n">
         <v>-24775736.60936207</v>
       </c>
-      <c r="CQ47" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CR47" s="8" t="n">
         <v>0</v>
       </c>
@@ -21449,6 +21587,9 @@
         <v>0</v>
       </c>
       <c r="EP47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ47" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21540,18 +21681,18 @@
       <c r="AA48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB48" s="9" t="n">
+      <c r="AB48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="9" t="n">
         <v>-894803.7308454514</v>
       </c>
-      <c r="AC48" s="9" t="n">
+      <c r="AD48" s="9" t="n">
         <v>-134166959.7655535</v>
       </c>
-      <c r="AD48" s="9" t="n">
+      <c r="AE48" s="9" t="n">
         <v>-57353694.56708431</v>
       </c>
-      <c r="AE48" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF48" s="8" t="n">
         <v>0</v>
       </c>
@@ -21645,15 +21786,15 @@
       <c r="BJ48" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BK48" s="9" t="n">
+      <c r="BK48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL48" s="9" t="n">
         <v>-134526385.6440783</v>
       </c>
-      <c r="BL48" s="9" t="n">
+      <c r="BM48" s="9" t="n">
         <v>-57353694.56708431</v>
       </c>
-      <c r="BM48" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BN48" s="8" t="n">
         <v>0</v>
       </c>
@@ -21895,6 +22036,9 @@
         <v>0</v>
       </c>
       <c r="EP48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ48" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21986,27 +22130,27 @@
       <c r="AA49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB49" s="9" t="n">
+      <c r="AB49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="9" t="n">
         <v>-452566.8108463287</v>
       </c>
-      <c r="AC49" s="9" t="n">
+      <c r="AD49" s="9" t="n">
         <v>-1256825.250089169</v>
       </c>
-      <c r="AD49" s="9" t="n">
+      <c r="AE49" s="9" t="n">
         <v>-4897182.584106922</v>
       </c>
-      <c r="AE49" s="9" t="n">
+      <c r="AF49" s="9" t="n">
         <v>-108854685.8868003</v>
       </c>
-      <c r="AF49" s="9" t="n">
+      <c r="AG49" s="9" t="n">
         <v>-266195000.8529425</v>
       </c>
-      <c r="AG49" s="9" t="n">
+      <c r="AH49" s="9" t="n">
         <v>-5501626.986265182</v>
       </c>
-      <c r="AH49" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI49" s="8" t="n">
         <v>0</v>
       </c>
@@ -22091,21 +22235,21 @@
       <c r="BJ49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BK49" s="9" t="n">
+      <c r="BK49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL49" s="9" t="n">
         <v>-1438243.736922741</v>
       </c>
-      <c r="BL49" s="9" t="n">
+      <c r="BM49" s="9" t="n">
         <v>-59326061.50478125</v>
       </c>
-      <c r="BM49" s="9" t="n">
+      <c r="BN49" s="9" t="n">
         <v>-320617239.0791774</v>
       </c>
-      <c r="BN49" s="9" t="n">
+      <c r="BO49" s="9" t="n">
         <v>-5501626.986563206</v>
       </c>
-      <c r="BO49" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BP49" s="8" t="n">
         <v>0</v>
       </c>
@@ -22341,6 +22485,9 @@
         <v>0</v>
       </c>
       <c r="EP49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ49" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22432,27 +22579,27 @@
       <c r="AA50" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB50" s="9" t="n">
+      <c r="AB50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="9" t="n">
         <v>-60287.59703040123</v>
       </c>
-      <c r="AC50" s="9" t="n">
+      <c r="AD50" s="9" t="n">
         <v>-167209.7590193152</v>
       </c>
-      <c r="AD50" s="9" t="n">
+      <c r="AE50" s="9" t="n">
         <v>-649961.773045361</v>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AF50" s="9" t="n">
         <v>-14375878.49285454</v>
       </c>
-      <c r="AF50" s="9" t="n">
+      <c r="AG50" s="9" t="n">
         <v>-35098536.16107255</v>
       </c>
-      <c r="AG50" s="9" t="n">
+      <c r="AH50" s="9" t="n">
         <v>-724563.4739100933</v>
       </c>
-      <c r="AH50" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI50" s="8" t="n">
         <v>0</v>
       </c>
@@ -22597,21 +22744,21 @@
       <c r="CD50" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CE50" s="9" t="n">
+      <c r="CE50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF50" s="9" t="n">
         <v>-191373.7157732248</v>
       </c>
-      <c r="CF50" s="9" t="n">
+      <c r="CG50" s="9" t="n">
         <v>-7838103.865087032</v>
       </c>
-      <c r="CG50" s="9" t="n">
+      <c r="CH50" s="9" t="n">
         <v>-42285801.74546689</v>
       </c>
-      <c r="CH50" s="9" t="n">
+      <c r="CI50" s="9" t="n">
         <v>-724563.4739100933</v>
       </c>
-      <c r="CI50" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CJ50" s="8" t="n">
         <v>0</v>
       </c>
@@ -22787,6 +22934,9 @@
         <v>0</v>
       </c>
       <c r="EP50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ50" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22878,27 +23028,27 @@
       <c r="AA51" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9" t="n">
         <v>-33046.83174937963</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AD51" s="9" t="n">
         <v>-91220.14846652746</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AE51" s="9" t="n">
         <v>-351432.2866499424</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AF51" s="9" t="n">
         <v>-7630927.784536034</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AG51" s="9" t="n">
         <v>-18519801.12535879</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AH51" s="9" t="n">
         <v>-380668.868701905</v>
       </c>
-      <c r="AH51" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI51" s="8" t="n">
         <v>0</v>
       </c>
@@ -23043,21 +23193,21 @@
       <c r="CD51" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CE51" s="9" t="n">
+      <c r="CE51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" s="9" t="n">
         <v>-104459.0344838798</v>
       </c>
-      <c r="CF51" s="9" t="n">
+      <c r="CG51" s="9" t="n">
         <v>-4167003.845237195</v>
       </c>
-      <c r="CG51" s="9" t="n">
+      <c r="CH51" s="9" t="n">
         <v>-22334908.39933977</v>
       </c>
-      <c r="CH51" s="9" t="n">
+      <c r="CI51" s="9" t="n">
         <v>-380668.868701905</v>
       </c>
-      <c r="CI51" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CJ51" s="8" t="n">
         <v>0</v>
       </c>
@@ -23233,6 +23383,9 @@
         <v>0</v>
       </c>
       <c r="EP51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ51" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23324,27 +23477,27 @@
       <c r="AA52" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB52" s="9" t="n">
+      <c r="AB52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="9" t="n">
         <v>-1305942.093282938</v>
       </c>
-      <c r="AC52" s="9" t="n">
+      <c r="AD52" s="9" t="n">
         <v>-3607500.064298511</v>
       </c>
-      <c r="AD52" s="9" t="n">
+      <c r="AE52" s="9" t="n">
         <v>-13791950.42595267</v>
       </c>
-      <c r="AE52" s="9" t="n">
+      <c r="AF52" s="9" t="n">
         <v>-29525526.93724632</v>
       </c>
-      <c r="AF52" s="9" t="n">
+      <c r="AG52" s="9" t="n">
         <v>-38688639.97675478</v>
       </c>
-      <c r="AG52" s="9" t="n">
+      <c r="AH52" s="9" t="n">
         <v>-3015600.505545735</v>
       </c>
-      <c r="AH52" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI52" s="8" t="n">
         <v>0</v>
       </c>
@@ -23441,21 +23594,21 @@
       <c r="BN52" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="BO52" s="9" t="n">
+      <c r="BO52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" s="9" t="n">
         <v>-4130147.254392505</v>
       </c>
-      <c r="BP52" s="9" t="n">
+      <c r="BQ52" s="9" t="n">
         <v>-28554907.61138499</v>
       </c>
-      <c r="BQ52" s="9" t="n">
+      <c r="BR52" s="9" t="n">
         <v>-53451129.14226949</v>
       </c>
-      <c r="BR52" s="9" t="n">
+      <c r="BS52" s="9" t="n">
         <v>-3015600.50547123</v>
       </c>
-      <c r="BS52" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="BT52" s="8" t="n">
         <v>0</v>
       </c>
@@ -23679,6 +23832,9 @@
         <v>0</v>
       </c>
       <c r="EP52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ52" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23770,27 +23926,27 @@
       <c r="AA53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB53" s="9" t="n">
+      <c r="AB53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9" t="n">
         <v>195466.2317037582</v>
       </c>
-      <c r="AC53" s="9" t="n">
+      <c r="AD53" s="9" t="n">
         <v>538366.9961802661</v>
       </c>
-      <c r="AD53" s="9" t="n">
+      <c r="AE53" s="9" t="n">
         <v>2046787.464888766</v>
       </c>
-      <c r="AE53" s="9" t="n">
+      <c r="AF53" s="9" t="n">
         <v>4347640.860779211</v>
       </c>
-      <c r="AF53" s="9" t="n">
+      <c r="AG53" s="9" t="n">
         <v>5646062.253694981</v>
       </c>
-      <c r="AG53" s="9" t="n">
+      <c r="AH53" s="9" t="n">
         <v>438442.2431606799</v>
       </c>
-      <c r="AH53" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI53" s="8" t="n">
         <v>0</v>
       </c>
@@ -23947,21 +24103,21 @@
       <c r="CH53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="CI53" s="9" t="n">
+      <c r="CI53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ53" s="9" t="n">
         <v>616573.8055296242</v>
       </c>
-      <c r="CJ53" s="9" t="n">
+      <c r="CK53" s="9" t="n">
         <v>4220636.19479537</v>
       </c>
-      <c r="CK53" s="9" t="n">
+      <c r="CL53" s="9" t="n">
         <v>7819842.800404876</v>
       </c>
-      <c r="CL53" s="9" t="n">
+      <c r="CM53" s="9" t="n">
         <v>438442.2431606799</v>
       </c>
-      <c r="CM53" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="CN53" s="8" t="n">
         <v>0</v>
       </c>
@@ -24125,6 +24281,9 @@
         <v>0</v>
       </c>
       <c r="EP53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ53" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24495,82 +24654,85 @@
       <c r="DP54" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DQ54" s="9" t="n">
+      <c r="DQ54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR54" s="9" t="n">
         <v>2090050</v>
       </c>
-      <c r="DR54" s="9" t="n">
+      <c r="DS54" s="9" t="n">
         <v>722650</v>
       </c>
-      <c r="DS54" s="9" t="n">
+      <c r="DT54" s="9" t="n">
         <v>538675</v>
       </c>
-      <c r="DT54" s="9" t="n">
+      <c r="DU54" s="9" t="n">
         <v>548075</v>
       </c>
-      <c r="DU54" s="9" t="n">
+      <c r="DV54" s="9" t="n">
         <v>1659950</v>
       </c>
-      <c r="DV54" s="9" t="n">
+      <c r="DW54" s="9" t="n">
         <v>992650</v>
       </c>
-      <c r="DW54" s="9" t="n">
+      <c r="DX54" s="9" t="n">
         <v>1590500</v>
       </c>
-      <c r="DX54" s="9" t="n">
+      <c r="DY54" s="9" t="n">
         <v>237450</v>
       </c>
-      <c r="DY54" s="9" t="n">
+      <c r="DZ54" s="9" t="n">
         <v>556950</v>
       </c>
-      <c r="DZ54" s="9" t="n">
+      <c r="EA54" s="9" t="n">
         <v>562475</v>
       </c>
-      <c r="EA54" s="9" t="n">
+      <c r="EB54" s="9" t="n">
         <v>1799475</v>
       </c>
-      <c r="EB54" s="9" t="n">
+      <c r="EC54" s="9" t="n">
         <v>3723925</v>
       </c>
-      <c r="EC54" s="9" t="n">
+      <c r="ED54" s="9" t="n">
         <v>985900</v>
       </c>
-      <c r="ED54" s="9" t="n">
+      <c r="EE54" s="9" t="n">
         <v>1382050</v>
       </c>
-      <c r="EE54" s="9" t="n">
+      <c r="EF54" s="9" t="n">
         <v>447775</v>
       </c>
-      <c r="EF54" s="9" t="n">
+      <c r="EG54" s="9" t="n">
         <v>733375</v>
       </c>
-      <c r="EG54" s="9" t="n">
+      <c r="EH54" s="9" t="n">
         <v>705950</v>
       </c>
-      <c r="EH54" s="9" t="n">
+      <c r="EI54" s="9" t="n">
         <v>1338825</v>
       </c>
-      <c r="EI54" s="9" t="n">
+      <c r="EJ54" s="9" t="n">
         <v>680425</v>
       </c>
-      <c r="EJ54" s="9" t="n">
+      <c r="EK54" s="9" t="n">
         <v>444650</v>
       </c>
-      <c r="EK54" s="9" t="n">
+      <c r="EL54" s="9" t="n">
         <v>964500.0000000001</v>
       </c>
-      <c r="EL54" s="9" t="n">
+      <c r="EM54" s="9" t="n">
         <v>428425</v>
       </c>
-      <c r="EM54" s="9" t="n">
+      <c r="EN54" s="9" t="n">
         <v>728650</v>
       </c>
-      <c r="EN54" s="9" t="n">
+      <c r="EO54" s="9" t="n">
         <v>398750</v>
       </c>
-      <c r="EO54" s="9" t="n">
+      <c r="EP54" s="9" t="n">
         <v>737850</v>
       </c>
-      <c r="EP54" s="8" t="n">
+      <c r="EQ54" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24665,14 +24827,14 @@
       <c r="AB55" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="8" t="n">
-        <v>0</v>
+      <c r="AC55" s="9" t="n">
+        <v>88110.06438236291</v>
+      </c>
+      <c r="AD55" s="9" t="n">
+        <v>6130925.168648104</v>
+      </c>
+      <c r="AE55" s="9" t="n">
+        <v>15034949.6318114</v>
       </c>
       <c r="AF55" s="8" t="n">
         <v>0</v>
@@ -25017,6 +25179,9 @@
         <v>0</v>
       </c>
       <c r="EP55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ55" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25387,82 +25552,85 @@
       <c r="DP56" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DQ56" s="9" t="n">
+      <c r="DQ56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR56" s="9" t="n">
         <v>1254030</v>
       </c>
-      <c r="DR56" s="9" t="n">
+      <c r="DS56" s="9" t="n">
         <v>433590</v>
       </c>
-      <c r="DS56" s="9" t="n">
+      <c r="DT56" s="9" t="n">
         <v>323205</v>
       </c>
-      <c r="DT56" s="9" t="n">
+      <c r="DU56" s="9" t="n">
         <v>328844.9999999999</v>
       </c>
-      <c r="DU56" s="9" t="n">
+      <c r="DV56" s="9" t="n">
         <v>995970</v>
       </c>
-      <c r="DV56" s="9" t="n">
+      <c r="DW56" s="9" t="n">
         <v>595590</v>
       </c>
-      <c r="DW56" s="9" t="n">
+      <c r="DX56" s="9" t="n">
         <v>954299.9999999999</v>
       </c>
-      <c r="DX56" s="9" t="n">
+      <c r="DY56" s="9" t="n">
         <v>142470</v>
       </c>
-      <c r="DY56" s="9" t="n">
+      <c r="DZ56" s="9" t="n">
         <v>334170</v>
       </c>
-      <c r="DZ56" s="9" t="n">
+      <c r="EA56" s="9" t="n">
         <v>337485</v>
       </c>
-      <c r="EA56" s="9" t="n">
+      <c r="EB56" s="9" t="n">
         <v>1079685</v>
       </c>
-      <c r="EB56" s="9" t="n">
+      <c r="EC56" s="9" t="n">
         <v>2234355</v>
       </c>
-      <c r="EC56" s="9" t="n">
+      <c r="ED56" s="9" t="n">
         <v>591540</v>
       </c>
-      <c r="ED56" s="9" t="n">
+      <c r="EE56" s="9" t="n">
         <v>829230</v>
       </c>
-      <c r="EE56" s="9" t="n">
+      <c r="EF56" s="9" t="n">
         <v>268665</v>
       </c>
-      <c r="EF56" s="9" t="n">
+      <c r="EG56" s="9" t="n">
         <v>440025</v>
       </c>
-      <c r="EG56" s="9" t="n">
+      <c r="EH56" s="9" t="n">
         <v>423570</v>
       </c>
-      <c r="EH56" s="9" t="n">
+      <c r="EI56" s="9" t="n">
         <v>803295</v>
       </c>
-      <c r="EI56" s="9" t="n">
+      <c r="EJ56" s="9" t="n">
         <v>408255</v>
       </c>
-      <c r="EJ56" s="9" t="n">
+      <c r="EK56" s="9" t="n">
         <v>266790</v>
       </c>
-      <c r="EK56" s="9" t="n">
+      <c r="EL56" s="9" t="n">
         <v>578700</v>
       </c>
-      <c r="EL56" s="9" t="n">
+      <c r="EM56" s="9" t="n">
         <v>257055</v>
       </c>
-      <c r="EM56" s="9" t="n">
+      <c r="EN56" s="9" t="n">
         <v>437190</v>
       </c>
-      <c r="EN56" s="9" t="n">
+      <c r="EO56" s="9" t="n">
         <v>239250</v>
       </c>
-      <c r="EO56" s="9" t="n">
+      <c r="EP56" s="9" t="n">
         <v>442710</v>
       </c>
-      <c r="EP56" s="8" t="n">
+      <c r="EQ56" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25557,17 +25725,17 @@
       <c r="AB57" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="8" t="n">
-        <v>0</v>
+      <c r="AC57" s="9" t="n">
+        <v>52520.50896586979</v>
+      </c>
+      <c r="AD57" s="9" t="n">
+        <v>146034.6940973522</v>
+      </c>
+      <c r="AE57" s="9" t="n">
+        <v>14488485.81887319</v>
+      </c>
+      <c r="AF57" s="9" t="n">
+        <v>1669397.589147081</v>
       </c>
       <c r="AG57" s="8" t="n">
         <v>0</v>
@@ -25909,6 +26077,9 @@
         <v>0</v>
       </c>
       <c r="EP57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ57" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26279,82 +26450,85 @@
       <c r="DP58" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="DQ58" s="9" t="n">
+      <c r="DQ58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR58" s="9" t="n">
         <v>836020.0000000001</v>
       </c>
-      <c r="DR58" s="9" t="n">
+      <c r="DS58" s="9" t="n">
         <v>289060</v>
       </c>
-      <c r="DS58" s="9" t="n">
+      <c r="DT58" s="9" t="n">
         <v>215470</v>
       </c>
-      <c r="DT58" s="9" t="n">
+      <c r="DU58" s="9" t="n">
         <v>219230</v>
       </c>
-      <c r="DU58" s="9" t="n">
+      <c r="DV58" s="9" t="n">
         <v>663980</v>
       </c>
-      <c r="DV58" s="9" t="n">
+      <c r="DW58" s="9" t="n">
         <v>397060</v>
       </c>
-      <c r="DW58" s="9" t="n">
+      <c r="DX58" s="9" t="n">
         <v>636200</v>
       </c>
-      <c r="DX58" s="9" t="n">
+      <c r="DY58" s="9" t="n">
         <v>94980</v>
       </c>
-      <c r="DY58" s="9" t="n">
+      <c r="DZ58" s="9" t="n">
         <v>222780</v>
       </c>
-      <c r="DZ58" s="9" t="n">
+      <c r="EA58" s="9" t="n">
         <v>224990</v>
       </c>
-      <c r="EA58" s="9" t="n">
+      <c r="EB58" s="9" t="n">
         <v>719790</v>
       </c>
-      <c r="EB58" s="9" t="n">
+      <c r="EC58" s="9" t="n">
         <v>1489570</v>
       </c>
-      <c r="EC58" s="9" t="n">
+      <c r="ED58" s="9" t="n">
         <v>394360</v>
       </c>
-      <c r="ED58" s="9" t="n">
+      <c r="EE58" s="9" t="n">
         <v>552820</v>
       </c>
-      <c r="EE58" s="9" t="n">
+      <c r="EF58" s="9" t="n">
         <v>179110</v>
       </c>
-      <c r="EF58" s="9" t="n">
+      <c r="EG58" s="9" t="n">
         <v>293350</v>
       </c>
-      <c r="EG58" s="9" t="n">
+      <c r="EH58" s="9" t="n">
         <v>282380</v>
       </c>
-      <c r="EH58" s="9" t="n">
+      <c r="EI58" s="9" t="n">
         <v>535530</v>
       </c>
-      <c r="EI58" s="9" t="n">
+      <c r="EJ58" s="9" t="n">
         <v>272170</v>
       </c>
-      <c r="EJ58" s="9" t="n">
+      <c r="EK58" s="9" t="n">
         <v>177860</v>
       </c>
-      <c r="EK58" s="9" t="n">
+      <c r="EL58" s="9" t="n">
         <v>385800.0000000001</v>
       </c>
-      <c r="EL58" s="9" t="n">
+      <c r="EM58" s="9" t="n">
         <v>171370</v>
       </c>
-      <c r="EM58" s="9" t="n">
+      <c r="EN58" s="9" t="n">
         <v>291460</v>
       </c>
-      <c r="EN58" s="9" t="n">
+      <c r="EO58" s="9" t="n">
         <v>159500</v>
       </c>
-      <c r="EO58" s="9" t="n">
+      <c r="EP58" s="9" t="n">
         <v>295140</v>
       </c>
-      <c r="EP58" s="8" t="n">
+      <c r="EQ58" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26449,17 +26623,17 @@
       <c r="AB59" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="8" t="n">
-        <v>0</v>
+      <c r="AC59" s="9" t="n">
+        <v>32025.41486757582</v>
+      </c>
+      <c r="AD59" s="9" t="n">
+        <v>98716.77390549393</v>
+      </c>
+      <c r="AE59" s="9" t="n">
+        <v>8287941.310101132</v>
+      </c>
+      <c r="AF59" s="9" t="n">
+        <v>5343331.430225362</v>
       </c>
       <c r="AG59" s="8" t="n">
         <v>0</v>
@@ -26801,6 +26975,9 @@
         <v>0</v>
       </c>
       <c r="EP59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ59" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26892,27 +27069,27 @@
       <c r="AA60" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB60" s="9" t="n">
+      <c r="AB60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="9" t="n">
         <v>-36925.98122029267</v>
       </c>
-      <c r="AC60" s="9" t="n">
+      <c r="AD60" s="9" t="n">
         <v>-163641.8782311466</v>
       </c>
-      <c r="AD60" s="9" t="n">
+      <c r="AE60" s="9" t="n">
         <v>-584019.6619715244</v>
       </c>
-      <c r="AE60" s="9" t="n">
+      <c r="AF60" s="9" t="n">
         <v>-1301159.898446258</v>
       </c>
-      <c r="AF60" s="9" t="n">
+      <c r="AG60" s="9" t="n">
         <v>-34809684.70648804</v>
       </c>
-      <c r="AG60" s="9" t="n">
+      <c r="AH60" s="9" t="n">
         <v>-40579932.67286974</v>
       </c>
-      <c r="AH60" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="AI60" s="8" t="n">
         <v>0</v>
       </c>
@@ -27247,6 +27424,9 @@
         <v>0</v>
       </c>
       <c r="EP60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ60" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27305,23 +27485,23 @@
       <c r="P61" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="Q61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v>0</v>
+      <c r="Q61" s="9" t="n">
+        <v>36919.66892915843</v>
+      </c>
+      <c r="R61" s="9" t="n">
+        <v>163551.0753885683</v>
+      </c>
+      <c r="S61" s="9" t="n">
+        <v>583914.1927026503</v>
+      </c>
+      <c r="T61" s="9" t="n">
+        <v>1301929.72139298</v>
+      </c>
+      <c r="U61" s="9" t="n">
+        <v>34534624.4598943</v>
+      </c>
+      <c r="V61" s="9" t="n">
+        <v>40246655.98069532</v>
       </c>
       <c r="W61" s="8" t="n">
         <v>0</v>
@@ -27338,8 +27518,8 @@
       <c r="AA61" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="AB61" s="8" t="n">
-        <v>0</v>
+      <c r="AB61" s="9" t="n">
+        <v>76860080.82728833</v>
       </c>
       <c r="AC61" s="8" t="n">
         <v>0</v>
@@ -27692,7 +27872,10 @@
       <c r="EO61" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="EP61" s="9" t="n">
+      <c r="EP61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ61" s="9" t="n">
         <v>-27290000</v>
       </c>
     </row>
@@ -28138,7 +28321,10 @@
       <c r="EO62" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="EP62" s="9" t="n">
+      <c r="EP62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ62" s="9" t="n">
         <v>6822500</v>
       </c>
     </row>
@@ -28584,7 +28770,10 @@
       <c r="EO63" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="EP63" s="9" t="n">
+      <c r="EP63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ63" s="9" t="n">
         <v>4093500</v>
       </c>
     </row>
@@ -29030,7 +29219,10 @@
       <c r="EO64" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="EP64" s="9" t="n">
+      <c r="EP64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ64" s="9" t="n">
         <v>2729000</v>
       </c>
     </row>
@@ -29045,7 +29237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -29320,7 +29512,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
@@ -29330,7 +29522,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>-15528.3718259831</v>
+        <v>21391.29710317533</v>
       </c>
     </row>
     <row r="34">
@@ -29340,7 +29532,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>-35558.01941733847</v>
+        <v>127993.0559712298</v>
       </c>
     </row>
     <row r="35">
@@ -29350,7 +29542,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>-146877.4217753044</v>
+        <v>437036.7709273459</v>
       </c>
     </row>
     <row r="36">
@@ -29360,7 +29552,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>-332323.7462250909</v>
+        <v>969605.9751678894</v>
       </c>
     </row>
     <row r="37">
@@ -29370,7 +29562,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>-819321.8106870588</v>
+        <v>33715302.64920724</v>
       </c>
     </row>
     <row r="38">
@@ -29380,7 +29572,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>-42332638.66245601</v>
+        <v>-2085982.681760695</v>
       </c>
     </row>
     <row r="39">
@@ -29436,1190 +29628,1200 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GIRR_USD_0.25Y</t>
+          <t>GIRR_GBP_XCCY_BASIS</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>-6548407.386871117</v>
+        <v>76860080.82728833</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GIRR_USD_0.5Y</t>
+          <t>GIRR_USD_0.25Y</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>-150155538.324676</v>
+        <v>-6375751.398655307</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GIRR_USD_1.0Y</t>
+          <t>GIRR_USD_0.5Y</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>-123987737.4558528</v>
+        <v>-143779861.6880251</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GIRR_USD_2.0Y</t>
+          <t>GIRR_USD_1.0Y</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>-266634513.9397797</v>
+        <v>-86176360.69506706</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GIRR_USD_3.0Y</t>
+          <t>GIRR_USD_2.0Y</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>-774247567.2031664</v>
+        <v>-259621784.9204072</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GIRR_USD_5.0Y</t>
+          <t>GIRR_USD_3.0Y</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>-504680220.743346</v>
+        <v>-774247567.2031664</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GIRR_USD_10.0Y</t>
+          <t>GIRR_USD_5.0Y</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>-462291533.6762248</v>
+        <v>-504680220.743346</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_3_0.5Y</t>
+          <t>GIRR_USD_10.0Y</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>-626772.1608138571</v>
+        <v>-462291533.6762248</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_3_1.0Y</t>
+          <t>CSR_NONSEC_3_0.5Y</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>-965547.9734009873</v>
+        <v>-626772.1608138571</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_3_3.0Y</t>
+          <t>CSR_NONSEC_3_1.0Y</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>-1131584.479480352</v>
+        <v>-965547.9734009873</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_4_0.5Y</t>
+          <t>CSR_NONSEC_3_3.0Y</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>-48984.50566668088</v>
+        <v>-1131584.479480352</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_4_1.0Y</t>
+          <t>CSR_NONSEC_4_0.5Y</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>-1751875.467743844</v>
+        <v>-48984.50566668088</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_4_3.0Y</t>
+          <t>CSR_NONSEC_4_1.0Y</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>-6461920.142134431</v>
+        <v>-1751875.467743844</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_4_5.0Y</t>
+          <t>CSR_NONSEC_4_3.0Y</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>-2692678.27078346</v>
+        <v>-6461920.142134431</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_5_0.5Y</t>
+          <t>CSR_NONSEC_4_5.0Y</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>-27160.37135962779</v>
+        <v>-2692678.27078346</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_5_1.0Y</t>
+          <t>CSR_NONSEC_5_0.5Y</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>-1013897.164923378</v>
+        <v>-27160.37135962779</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_5_3.0Y</t>
+          <t>CSR_NONSEC_5_1.0Y</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>-1264612.555266296</v>
+        <v>-1013897.164923378</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_5_5.0Y</t>
+          <t>CSR_NONSEC_5_3.0Y</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>-4914173.419151098</v>
+        <v>-1264612.555266296</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_5_10.0Y</t>
+          <t>CSR_NONSEC_5_5.0Y</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>-3181693.338927004</v>
+        <v>-4914173.419151098</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_6_0.5Y</t>
+          <t>CSR_NONSEC_5_10.0Y</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>-71423.63033551647</v>
+        <v>-3181693.338927004</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_6_1.0Y</t>
+          <t>CSR_NONSEC_6_0.5Y</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>-2212209.744191227</v>
+        <v>-71423.63033551647</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_6_3.0Y</t>
+          <t>CSR_NONSEC_6_1.0Y</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>-9107757.246416155</v>
+        <v>-2212209.744191227</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_6_5.0Y</t>
+          <t>CSR_NONSEC_6_3.0Y</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>-2085945.519251481</v>
+        <v>-9107757.246416155</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_7_0.5Y</t>
+          <t>CSR_NONSEC_6_5.0Y</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>-112067.0334829015</v>
+        <v>-2085945.519251481</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_7_1.0Y</t>
+          <t>CSR_NONSEC_7_0.5Y</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>-1648532.557447538</v>
+        <v>-112067.0334829015</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_7_3.0Y</t>
+          <t>CSR_NONSEC_7_1.0Y</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>-1580878.632474651</v>
+        <v>-1648532.557447538</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CSR_NONSEC_7_5.0Y</t>
+          <t>CSR_NONSEC_7_3.0Y</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>-2077793.972451104</v>
+        <v>-1580878.632474651</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_1_0.5Y</t>
+          <t>CSR_NONSEC_7_5.0Y</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>-1104389.242455363</v>
+        <v>-2077793.972451104</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_1_1.0Y</t>
+          <t>CSR_SEC_NONCTP_1_0.5Y</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>-11181740.66208303</v>
+        <v>-1104389.242455363</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_1_3.0Y</t>
+          <t>CSR_SEC_NONCTP_1_1.0Y</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>-81814499.41888452</v>
+        <v>-11181740.66208303</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_4_0.5Y</t>
+          <t>CSR_SEC_NONCTP_1_3.0Y</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>-1031837.042178959</v>
+        <v>-81814499.41888452</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_4_1.0Y</t>
+          <t>CSR_SEC_NONCTP_4_0.5Y</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>-7316613.178057596</v>
+        <v>-1031837.042178959</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_4_3.0Y</t>
+          <t>CSR_SEC_NONCTP_4_1.0Y</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>-21686101.08996741</v>
+        <v>-7316613.178057596</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_4_5.0Y</t>
+          <t>CSR_SEC_NONCTP_4_3.0Y</t>
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>-241078028.0365795</v>
+        <v>-21686101.08996741</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_4_10.0Y</t>
+          <t>CSR_SEC_NONCTP_4_5.0Y</t>
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>-412593339.2532542</v>
+        <v>-241078028.0365795</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_6_0.5Y</t>
+          <t>CSR_SEC_NONCTP_4_10.0Y</t>
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>-135964629.381001</v>
+        <v>-412593339.2532542</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_6_1.0Y</t>
+          <t>CSR_SEC_NONCTP_6_0.5Y</t>
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>-116679756.0718656</v>
+        <v>-135964629.381001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_6_3.0Y</t>
+          <t>CSR_SEC_NONCTP_6_1.0Y</t>
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>-320617239.0791774</v>
+        <v>-116679756.0718656</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_6_5.0Y</t>
+          <t>CSR_SEC_NONCTP_6_3.0Y</t>
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>-5501626.986563206</v>
+        <v>-320617239.0791774</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_7_0.5Y</t>
+          <t>CSR_SEC_NONCTP_6_5.0Y</t>
         </is>
       </c>
       <c r="B83" s="12" t="n">
-        <v>-4130147.254392505</v>
+        <v>-5501626.986563206</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_7_1.0Y</t>
+          <t>CSR_SEC_NONCTP_7_0.5Y</t>
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>-28554907.61138499</v>
+        <v>-4130147.254392505</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_7_3.0Y</t>
+          <t>CSR_SEC_NONCTP_7_1.0Y</t>
         </is>
       </c>
       <c r="B85" s="12" t="n">
-        <v>-53451129.14226949</v>
+        <v>-28554907.61138499</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_7_5.0Y</t>
+          <t>CSR_SEC_NONCTP_7_3.0Y</t>
         </is>
       </c>
       <c r="B86" s="12" t="n">
-        <v>-3015600.50547123</v>
+        <v>-53451129.14226949</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_8_0.5Y</t>
+          <t>CSR_SEC_NONCTP_7_5.0Y</t>
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>-9007085.128128529</v>
+        <v>-3015600.50547123</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_8_1.0Y</t>
+          <t>CSR_SEC_NONCTP_8_0.5Y</t>
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>-61838026.80522203</v>
+        <v>-9007085.128128529</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_8_3.0Y</t>
+          <t>CSR_SEC_NONCTP_8_1.0Y</t>
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>-173716648.9610076</v>
+        <v>-61838026.80522203</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_8_5.0Y</t>
+          <t>CSR_SEC_NONCTP_8_3.0Y</t>
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>-91689947.71838188</v>
+        <v>-173716648.9610076</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_9_0.5Y</t>
+          <t>CSR_SEC_NONCTP_8_5.0Y</t>
         </is>
       </c>
       <c r="B91" s="12" t="n">
-        <v>-218481.6895006225</v>
+        <v>-91689947.71838188</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_9_1.0Y</t>
+          <t>CSR_SEC_NONCTP_9_0.5Y</t>
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>-2141899.353624322</v>
+        <v>-218481.6895006225</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_9_3.0Y</t>
+          <t>CSR_SEC_NONCTP_9_1.0Y</t>
         </is>
       </c>
       <c r="B93" s="12" t="n">
-        <v>-15407435.35295129</v>
+        <v>-2141899.353624322</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_12_0.5Y</t>
+          <t>CSR_SEC_NONCTP_9_3.0Y</t>
         </is>
       </c>
       <c r="B94" s="12" t="n">
-        <v>-141705.4025270045</v>
+        <v>-15407435.35295129</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_12_1.0Y</t>
+          <t>CSR_SEC_NONCTP_12_0.5Y</t>
         </is>
       </c>
       <c r="B95" s="12" t="n">
-        <v>-981367.1435788274</v>
+        <v>-141705.4025270045</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_12_3.0Y</t>
+          <t>CSR_SEC_NONCTP_12_1.0Y</t>
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>-2807073.642592877</v>
+        <v>-981367.1435788274</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_12_5.0Y</t>
+          <t>CSR_SEC_NONCTP_12_3.0Y</t>
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>-27587439.55498561</v>
+        <v>-2807073.642592877</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_12_10.0Y</t>
+          <t>CSR_SEC_NONCTP_12_5.0Y</t>
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>-46515278.08142826</v>
+        <v>-27587439.55498561</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_14_0.5Y</t>
+          <t>CSR_SEC_NONCTP_12_10.0Y</t>
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>-295832.7502571046</v>
+        <v>-46515278.08142826</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_14_1.0Y</t>
+          <t>CSR_SEC_NONCTP_14_0.5Y</t>
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>-12005107.71032423</v>
+        <v>-295832.7502571046</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_14_3.0Y</t>
+          <t>CSR_SEC_NONCTP_14_1.0Y</t>
         </is>
       </c>
       <c r="B101" s="12" t="n">
-        <v>-64620710.14480665</v>
+        <v>-12005107.71032423</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_14_5.0Y</t>
+          <t>CSR_SEC_NONCTP_14_3.0Y</t>
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>-1105232.342611998</v>
+        <v>-64620710.14480665</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_15_0.5Y</t>
+          <t>CSR_SEC_NONCTP_14_5.0Y</t>
         </is>
       </c>
       <c r="B103" s="12" t="n">
-        <v>616573.8055296242</v>
+        <v>-1105232.342611998</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_15_1.0Y</t>
+          <t>CSR_SEC_NONCTP_15_0.5Y</t>
         </is>
       </c>
       <c r="B104" s="12" t="n">
-        <v>4220636.19479537</v>
+        <v>616573.8055296242</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_15_3.0Y</t>
+          <t>CSR_SEC_NONCTP_15_1.0Y</t>
         </is>
       </c>
       <c r="B105" s="12" t="n">
-        <v>7819842.800404876</v>
+        <v>4220636.19479537</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_15_5.0Y</t>
+          <t>CSR_SEC_NONCTP_15_3.0Y</t>
         </is>
       </c>
       <c r="B106" s="12" t="n">
-        <v>438442.2431606799</v>
+        <v>7819842.800404876</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_16_0.5Y</t>
+          <t>CSR_SEC_NONCTP_15_5.0Y</t>
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>-615829.5128494501</v>
+        <v>438442.2431606799</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_16_1.0Y</t>
+          <t>CSR_SEC_NONCTP_16_0.5Y</t>
         </is>
       </c>
       <c r="B108" s="12" t="n">
-        <v>-7367943.724617362</v>
+        <v>-615829.5128494501</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_16_3.0Y</t>
+          <t>CSR_SEC_NONCTP_16_1.0Y</t>
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>-120830919.5543826</v>
+        <v>-7367943.724617362</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CSR_SEC_NONCTP_16_5.0Y</t>
+          <t>CSR_SEC_NONCTP_16_3.0Y</t>
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>-80521143.98028702</v>
+        <v>-120830919.5543826</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ_5_AMZN</t>
+          <t>CSR_SEC_NONCTP_16_5.0Y</t>
         </is>
       </c>
       <c r="B111" s="12" t="n">
-        <v>2580754.41</v>
+        <v>-80521143.98028702</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ_7_XOM</t>
+          <t>EQ_5_AMZN</t>
         </is>
       </c>
       <c r="B112" s="12" t="n">
-        <v>567812.96</v>
+        <v>2580754.41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ_8_AAPL</t>
+          <t>EQ_7_XOM</t>
         </is>
       </c>
       <c r="B113" s="12" t="n">
-        <v>3696642.18</v>
+        <v>567812.96</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ_8_BRK.B</t>
+          <t>EQ_8_AAPL</t>
         </is>
       </c>
       <c r="B114" s="12" t="n">
-        <v>656064.78</v>
+        <v>3696642.18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ_8_EQIX</t>
+          <t>EQ_8_BRK.B</t>
         </is>
       </c>
       <c r="B115" s="12" t="n">
-        <v>522491.32</v>
+        <v>656064.78</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ_8_GOOGL</t>
+          <t>EQ_8_EQIX</t>
         </is>
       </c>
       <c r="B116" s="12" t="n">
-        <v>3601681.25</v>
+        <v>522491.32</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ_8_JPM</t>
+          <t>EQ_8_GOOGL</t>
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>1128362.08</v>
+        <v>3601681.25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ_8_META</t>
+          <t>EQ_8_JPM</t>
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>1993874.75</v>
+        <v>1128362.08</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ_8_MSFT</t>
+          <t>EQ_8_META</t>
         </is>
       </c>
       <c r="B119" s="12" t="n">
-        <v>3599718.48</v>
+        <v>1993874.75</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ_8_NVDA</t>
+          <t>EQ_8_MSFT</t>
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>4902017.6</v>
+        <v>3599718.48</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ_12_SPX</t>
+          <t>EQ_8_NVDA</t>
         </is>
       </c>
       <c r="B121" s="12" t="n">
-        <v>-5235.452082694877</v>
+        <v>4902017.6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VEGA_EQ_12_SPX_0.5Y</t>
+          <t>EQ_12_SPX</t>
         </is>
       </c>
       <c r="B122" s="12" t="n">
-        <v>-1911456.506350513</v>
+        <v>-5235.452082694877</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VEGA_EQ_12_SPX_1.0Y</t>
+          <t>VEGA_EQ_12_SPX_0.5Y</t>
         </is>
       </c>
       <c r="B123" s="12" t="n">
-        <v>-2004105.853480715</v>
+        <v>-1911456.506350513</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VEGA_EQ_12_SPX_3.0Y</t>
+          <t>VEGA_EQ_12_SPX_1.0Y</t>
         </is>
       </c>
       <c r="B124" s="12" t="n">
-        <v>-146462.3815066698</v>
+        <v>-2004105.853480715</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_1.0Y_1.0Y</t>
+          <t>VEGA_EQ_12_SPX_3.0Y</t>
         </is>
       </c>
       <c r="B125" s="12" t="n">
-        <v>-80.83820524743329</v>
+        <v>-146462.3815066698</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_1.0Y_3.0Y</t>
+          <t>VEGA_GIRR_USD_1.0Y_1.0Y</t>
         </is>
       </c>
       <c r="B126" s="12" t="n">
-        <v>-81.05983158121653</v>
+        <v>-80.83820524743329</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_3.0Y_0.5Y</t>
+          <t>VEGA_GIRR_USD_1.0Y_3.0Y</t>
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>-0.2772749203155584</v>
+        <v>-81.05983158121653</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_3.0Y_1.0Y</t>
+          <t>VEGA_GIRR_USD_3.0Y_0.5Y</t>
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>-143.1067127309384</v>
+        <v>-0.2772749203155584</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_3.0Y_3.0Y</t>
+          <t>VEGA_GIRR_USD_3.0Y_1.0Y</t>
         </is>
       </c>
       <c r="B129" s="12" t="n">
-        <v>-35.65437257450877</v>
+        <v>-143.1067127309384</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_5.0Y_0.5Y</t>
+          <t>VEGA_GIRR_USD_3.0Y_3.0Y</t>
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>-0.1181361666351794</v>
+        <v>-35.65437257450877</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_5.0Y_1.0Y</t>
+          <t>VEGA_GIRR_USD_5.0Y_0.5Y</t>
         </is>
       </c>
       <c r="B131" s="12" t="n">
-        <v>-18.56691747167979</v>
+        <v>-0.1181361666351794</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VEGA_GIRR_USD_5.0Y_3.0Y</t>
+          <t>VEGA_GIRR_USD_5.0Y_1.0Y</t>
         </is>
       </c>
       <c r="B132" s="12" t="n">
-        <v>-0.4686380436460109</v>
+        <v>-18.56691747167979</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CURV_EQ_12_SPX_DN</t>
+          <t>VEGA_GIRR_USD_5.0Y_3.0Y</t>
         </is>
       </c>
       <c r="B133" s="12" t="n">
-        <v>-52893.01271429182</v>
+        <v>-0.4686380436460109</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CURV_EQ_12_SPX_UP</t>
+          <t>CURV_EQ_12_SPX_DN</t>
         </is>
       </c>
       <c r="B134" s="12" t="n">
-        <v>53872.70008700639</v>
+        <v>-52893.01271429182</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CURV_GIRR_USD_DN</t>
+          <t>CURV_EQ_12_SPX_UP</t>
         </is>
       </c>
       <c r="B135" s="12" t="n">
-        <v>31106.19403192937</v>
+        <v>53872.70008700639</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CURV_GIRR_USD_UP</t>
+          <t>CURV_GIRR_USD_DN</t>
         </is>
       </c>
       <c r="B136" s="12" t="n">
-        <v>-24423.60594240938</v>
+        <v>31106.19403192937</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>COMM_2_Brent_Crude_Oil</t>
+          <t>CURV_GIRR_USD_UP</t>
         </is>
       </c>
       <c r="B137" s="12" t="n">
-        <v>4180100.000000001</v>
+        <v>-24423.60594240938</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>COMM_2_Low_Sulphur_Gas_Oil</t>
+          <t>COMM_2_Brent_Crude_Oil</t>
         </is>
       </c>
       <c r="B138" s="12" t="n">
-        <v>1445300</v>
+        <v>4180100.000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>COMM_2_RBOB_Gasoline</t>
+          <t>COMM_2_Low_Sulphur_Gas_Oil</t>
         </is>
       </c>
       <c r="B139" s="12" t="n">
-        <v>1077350</v>
+        <v>1445300</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>COMM_2_ULS_Diesel</t>
+          <t>COMM_2_RBOB_Gasoline</t>
         </is>
       </c>
       <c r="B140" s="12" t="n">
-        <v>1096150</v>
+        <v>1077350</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COMM_2_WTI_Crude_Oil</t>
+          <t>COMM_2_ULS_Diesel</t>
         </is>
       </c>
       <c r="B141" s="12" t="n">
-        <v>3319900</v>
+        <v>1096150</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COMM_5_Aluminum</t>
+          <t>COMM_2_WTI_Crude_Oil</t>
         </is>
       </c>
       <c r="B142" s="12" t="n">
-        <v>1985300</v>
+        <v>3319900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>COMM_5_Copper</t>
+          <t>COMM_5_Aluminum</t>
         </is>
       </c>
       <c r="B143" s="12" t="n">
-        <v>3181000</v>
+        <v>1985300</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COMM_5_Lead</t>
+          <t>COMM_5_Copper</t>
         </is>
       </c>
       <c r="B144" s="12" t="n">
-        <v>474900</v>
+        <v>3181000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>COMM_5_Nickel</t>
+          <t>COMM_5_Lead</t>
         </is>
       </c>
       <c r="B145" s="12" t="n">
-        <v>1113900</v>
+        <v>474900</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COMM_5_Zinc</t>
+          <t>COMM_5_Nickel</t>
         </is>
       </c>
       <c r="B146" s="12" t="n">
-        <v>1124950</v>
+        <v>1113900</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>COMM_6_Natural_Gas</t>
+          <t>COMM_5_Zinc</t>
         </is>
       </c>
       <c r="B147" s="12" t="n">
-        <v>3598950</v>
+        <v>1124950</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COMM_7_Gold</t>
+          <t>COMM_6_Natural_Gas</t>
         </is>
       </c>
       <c r="B148" s="12" t="n">
-        <v>7447850</v>
+        <v>3598950</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COMM_7_Silver</t>
+          <t>COMM_7_Gold</t>
         </is>
       </c>
       <c r="B149" s="12" t="n">
-        <v>1971800</v>
+        <v>7447850</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COMM_8_Corn</t>
+          <t>COMM_7_Silver</t>
         </is>
       </c>
       <c r="B150" s="12" t="n">
-        <v>2764100</v>
+        <v>1971800</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>COMM_8_HRW_Wheat</t>
+          <t>COMM_8_Corn</t>
         </is>
       </c>
       <c r="B151" s="12" t="n">
-        <v>895550</v>
+        <v>2764100</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>COMM_8_Soybean_Meal</t>
+          <t>COMM_8_HRW_Wheat</t>
         </is>
       </c>
       <c r="B152" s="12" t="n">
-        <v>1466750</v>
+        <v>895550</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>COMM_8_Soybean_Oil</t>
+          <t>COMM_8_Soybean_Meal</t>
         </is>
       </c>
       <c r="B153" s="12" t="n">
-        <v>1411900</v>
+        <v>1466750</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>COMM_8_Soybeans</t>
+          <t>COMM_8_Soybean_Oil</t>
         </is>
       </c>
       <c r="B154" s="12" t="n">
-        <v>2677650</v>
+        <v>1411900</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>COMM_8_Wheat</t>
+          <t>COMM_8_Soybeans</t>
         </is>
       </c>
       <c r="B155" s="12" t="n">
-        <v>1360850</v>
+        <v>2677650</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>COMM_9_Lean_Hogs</t>
+          <t>COMM_8_Wheat</t>
         </is>
       </c>
       <c r="B156" s="12" t="n">
-        <v>889300</v>
+        <v>1360850</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>COMM_9_Live_Cattle</t>
+          <t>COMM_9_Lean_Hogs</t>
         </is>
       </c>
       <c r="B157" s="12" t="n">
-        <v>1929000</v>
+        <v>889300</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>COMM_10_Cocoa</t>
+          <t>COMM_9_Live_Cattle</t>
         </is>
       </c>
       <c r="B158" s="12" t="n">
-        <v>856850</v>
+        <v>1929000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>COMM_10_Coffee</t>
+          <t>COMM_10_Cocoa</t>
         </is>
       </c>
       <c r="B159" s="12" t="n">
-        <v>1457300</v>
+        <v>856850</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>COMM_10_Cotton</t>
+          <t>COMM_10_Coffee</t>
         </is>
       </c>
       <c r="B160" s="12" t="n">
-        <v>797500</v>
+        <v>1457300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>COMM_10_Sugar</t>
+          <t>COMM_10_Cotton</t>
         </is>
       </c>
       <c r="B161" s="12" t="n">
-        <v>1475700</v>
+        <v>797500</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>COMM_10_Sugar</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="n">
+        <v>1475700</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>FX_GBP/USD</t>
         </is>
       </c>
-      <c r="B162" s="12" t="n">
+      <c r="B163" s="12" t="n">
         <v>-13645000</v>
       </c>
     </row>
